--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O160"/>
+  <dimension ref="A1:O176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,27 +496,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/29/2026 2:23:36 PM</t>
+          <t>08/06/2026 9:31:18 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -545,38 +545,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/29/2026 1:29:51 PM</t>
+          <t>08/06/2026 4:43:28 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Brian Kelly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -584,48 +584,46 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N3" t="n">
+        <v>0.545</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/29/2026 12:50:14 PM</t>
+          <t>08/06/2026 7:30:46 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -643,32 +641,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/29/2026 10:04:25 AM</t>
+          <t>08/05/2026 6:26:33 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -682,48 +680,46 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" t="n">
+        <v>0.543</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/28/2026 4:27:30 PM</t>
+          <t>08/05/2026 3:11:07 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,27 +737,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/28/2026 3:53:58 PM</t>
+          <t>08/05/2026 2:24:40 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -772,7 +768,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,32 +786,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/28/2026 3:44:54 PM</t>
+          <t>08/04/2026 3:18:35 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -839,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/28/2026 1:51:55 PM</t>
+          <t>08/04/2026 9:00:55 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Khali Arrington</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,7 +860,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -878,42 +874,40 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.635</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/28/2026 11:42:07 AM</t>
+          <t>08/03/2026 7:20:40 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jerand Townsel</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -937,32 +931,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/28/2026 11:39:57 AM</t>
+          <t>08/03/2026 6:58:03 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -976,48 +970,46 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N11" t="n">
+        <v>0.491</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/28/2026 10:23:00 AM</t>
+          <t>08/03/2026 5:25:29 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1035,38 +1027,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/28/2026 9:57:45 AM</t>
+          <t>08/03/2026 3:02:06 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1084,27 +1076,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/28/2026 9:11:05 AM</t>
+          <t>08/03/2026 10:53:14 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1133,38 +1125,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/27/2026 5:42:13 PM</t>
+          <t>08/03/2026 10:05:29 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Defensive Driving, Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1172,40 +1164,42 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.529</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27/2026 2:04:05 PM</t>
+          <t>08/03/2026 9:13:14 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1229,32 +1223,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27/2026 12:00:04 PM</t>
+          <t>08/03/2026 8:39:15 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1278,32 +1272,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27/2026 8:57:57 AM</t>
+          <t>07/31/2026 7:09:03 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Kurt Purdie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1317,48 +1311,46 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N18" t="n">
+        <v>0.631</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24/2026 2:10:44 PM</t>
+          <t>07/31/2026 3:39:46 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1376,32 +1368,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24/2026 10:45:02 AM</t>
+          <t>07/31/2026 3:07:50 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1425,32 +1417,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24/2026 10:16:36 AM</t>
+          <t>07/31/2026 11:18:13 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1474,32 +1466,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:49 PM</t>
+          <t>07/31/2026 7:03:13 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1523,32 +1515,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 5:44:09 PM</t>
+          <t>07/29/2026 2:23:36 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1572,32 +1564,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21/2026 12:22:30 PM</t>
+          <t>07/29/2026 1:29:51 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUCK 85</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>John Boerger</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1621,38 +1613,38 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/21/2026 12:05:00 PM</t>
+          <t>07/29/2026 12:50:14 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1670,27 +1662,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/21/2026 11:52:20 AM</t>
+          <t>07/29/2026 10:04:25 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1719,32 +1711,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20/2026 3:59:36 PM</t>
+          <t>07/28/2026 4:27:30 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1768,7 +1760,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/16/2026 1:36:56 PM</t>
+          <t>07/28/2026 3:53:58 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1817,32 +1809,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/16/2026 1:17:23 PM</t>
+          <t>07/28/2026 3:44:54 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1866,32 +1858,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15/2026 4:52:33 PM</t>
+          <t>07/28/2026 1:51:55 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1915,38 +1907,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:43 PM</t>
+          <t>07/28/2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Jerand Townsel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1964,27 +1956,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:25 PM</t>
+          <t>07/28/2026 11:39:57 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2013,17 +2005,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15/2026 12:15:41 PM</t>
+          <t>07/28/2026 10:23:00 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2038,13 +2030,13 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2062,27 +2054,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15/2026 12:10:03 PM</t>
+          <t>07/28/2026 9:57:45 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2093,7 +2085,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2111,7 +2103,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/15/2026 6:28:32 AM</t>
+          <t>07/28/2026 9:11:05 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2121,7 +2113,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2136,7 +2128,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2160,32 +2152,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/14/2026 7:12:18 PM</t>
+          <t>07/27/2026 5:42:13 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Defensive Driving, Harsh Brake</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2199,48 +2191,46 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.529</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/14/2026 6:10:58 PM</t>
+          <t>07/27/2026 2:04:05 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2258,27 +2248,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/14/2026 5:39:20 PM</t>
+          <t>07/27/2026 12:00:04 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2289,7 +2279,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2307,27 +2297,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/14/2026 5:31:40 PM</t>
+          <t>07/27/2026 8:57:57 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2338,7 +2328,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2356,27 +2346,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/14/2026 11:46:20 AM</t>
+          <t>07/24/2026 2:10:44 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2405,32 +2395,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/14/2026 9:57:18 AM</t>
+          <t>07/24/2026 10:45:02 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2454,38 +2444,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/14/2026 9:13:03 AM</t>
+          <t>07/24/2026 10:16:36 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>truck 703</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2503,38 +2493,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/13/2026 2:41:35 PM</t>
+          <t>07/22/2026 8:57:49 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2552,38 +2542,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/13/2026 1:03:42 PM</t>
+          <t>07/22/2026 5:44:09 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Juan Santiago</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2601,38 +2591,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/13/2026 12:58:10 PM</t>
+          <t>07/21/2026 12:22:30 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 85</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>John Boerger</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2650,7 +2640,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/13/2026 12:48:08 PM</t>
+          <t>07/21/2026 12:05:00 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2660,7 +2650,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2699,32 +2689,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/13/2026 11:24:44 AM</t>
+          <t>07/21/2026 11:52:20 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2748,38 +2738,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/13/2026 10:27:59 AM</t>
+          <t>07/20/2026 3:59:36 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2797,32 +2787,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/12/2026 9:23:11 AM</t>
+          <t>07/16/2026 1:36:56 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OR 70</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2846,32 +2836,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/11/2026 8:35:15 AM</t>
+          <t>07/16/2026 1:17:23 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2895,27 +2885,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/10/2026 1:09:28 PM</t>
+          <t>07/15/2026 4:52:33 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2926,7 +2916,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2944,27 +2934,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/10/2026 5:25:49 AM</t>
+          <t>07/15/2026 3:06:43 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2993,38 +2983,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/10/2026 4:50:20 AM</t>
+          <t>07/15/2026 3:06:25 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3042,38 +3032,38 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/09/2026 7:53:06 PM</t>
+          <t>07/15/2026 12:15:41 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3081,35 +3071,37 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>0.671</v>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/09/2026 6:59:54 PM</t>
+          <t>07/15/2026 12:10:03 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3120,7 +3112,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3138,38 +3130,38 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/09/2026 6:21:15 PM</t>
+          <t>07/15/2026 6:28:32 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3187,32 +3179,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/09/2026 12:47:45 PM</t>
+          <t>07/14/2026 7:12:18 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3236,27 +3228,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/09/2026 11:55:07 AM</t>
+          <t>07/14/2026 6:10:58 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3267,7 +3259,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3285,32 +3277,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/08/2026 6:29:26 PM</t>
+          <t>07/14/2026 5:39:20 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3334,27 +3326,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/08/2026 11:40:54 AM</t>
+          <t>07/14/2026 5:31:40 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Truck 803</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3365,7 +3357,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3383,27 +3375,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/08/2026 10:12:05 AM</t>
+          <t>07/14/2026 11:46:20 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3432,32 +3424,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/07/2026 8:03:23 PM</t>
+          <t>07/14/2026 9:57:18 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3481,27 +3473,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/07/2026 6:38:32 PM</t>
+          <t>07/14/2026 9:13:03 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>truck 703</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3512,7 +3504,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3530,38 +3522,38 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/07/2026 2:48:19 PM</t>
+          <t>07/13/2026 2:41:35 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3579,38 +3571,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/06/2026 10:26:03 PM</t>
+          <t>07/13/2026 1:03:42 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Juan Santiago</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3628,17 +3620,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/06/2026 7:14:26 AM</t>
+          <t>07/13/2026 12:58:10 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3677,38 +3669,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/02/2026 5:15:10 PM</t>
+          <t>07/13/2026 12:48:08 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3726,32 +3718,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/02/2026 1:50:55 PM</t>
+          <t>07/13/2026 11:24:44 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3775,17 +3767,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/02/2026 12:25:36 PM</t>
+          <t>07/13/2026 10:27:59 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3800,7 +3792,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3824,38 +3816,38 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/02/2026 12:22:00 PM</t>
+          <t>07/12/2026 9:23:11 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3873,32 +3865,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/02/2026 12:00:30 PM</t>
+          <t>07/11/2026 8:35:15 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3912,15 +3904,17 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
-        <v>0.534</v>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/02/2026 11:56:44 AM</t>
+          <t>07/10/2026 1:09:28 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3930,7 +3924,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3969,27 +3963,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/02/2026 11:03:25 AM</t>
+          <t>07/10/2026 5:25:49 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRUCK 67</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4000,7 +3994,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4018,32 +4012,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/01/2026 6:08:17 PM</t>
+          <t>07/10/2026 4:50:20 AM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4067,38 +4061,38 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/01/2026 3:07:51 PM</t>
+          <t>07/09/2026 7:53:06 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4106,37 +4100,35 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N75" t="n">
+        <v>0.671</v>
       </c>
       <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/01/2026 1:29:57 PM</t>
+          <t>07/09/2026 6:59:54 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4165,27 +4157,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/01/2026 12:10:49 PM</t>
+          <t>07/09/2026 6:21:15 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4196,7 +4188,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4214,38 +4206,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/01/2026 9:29:37 AM</t>
+          <t>07/09/2026 12:47:45 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4253,46 +4245,48 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>0.708</v>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/30/2026 12:19:45 PM</t>
+          <t>07/09/2026 11:55:07 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4310,38 +4304,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/30/2026 8:20:51 AM</t>
+          <t>07/08/2026 6:29:26 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4359,32 +4353,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/29/2026 1:07:28 PM</t>
+          <t>07/08/2026 11:40:54 AM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 803</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4408,17 +4402,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/29/2026 4:14:57 AM</t>
+          <t>07/08/2026 10:12:05 AM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4433,7 +4427,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4457,38 +4451,38 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/26/2026 1:15:05 PM</t>
+          <t>07/07/2026 8:03:23 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4496,46 +4490,48 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
-        <v>0.597</v>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/26/2026 12:30:38 PM</t>
+          <t>07/07/2026 6:38:32 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4553,27 +4549,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/26/2026 11:53:52 AM</t>
+          <t>07/07/2026 2:48:19 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4584,7 +4580,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4602,32 +4598,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/26/2026 9:29:14 AM</t>
+          <t>07/06/2026 10:26:03 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -4651,32 +4647,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/25/2026 7:20:50 PM</t>
+          <t>07/06/2026 7:14:26 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4700,12 +4696,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/24/2026 6:03:00 PM</t>
+          <t>07/02/2026 5:15:10 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4725,7 +4721,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -4749,32 +4745,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/24/2026 11:16:24 AM</t>
+          <t>07/02/2026 1:50:55 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4798,32 +4794,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/24/2026 10:02:37 AM</t>
+          <t>07/02/2026 12:25:36 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4847,38 +4843,38 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/23/2026 11:23:16 AM</t>
+          <t>07/02/2026 12:22:00 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4896,32 +4892,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/20/2026 7:57:27 PM</t>
+          <t>07/02/2026 12:00:30 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -4935,48 +4931,46 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N92" t="n">
+        <v>0.534</v>
       </c>
       <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/19/2026 2:31:31 PM</t>
+          <t>07/02/2026 11:56:44 AM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4984,40 +4978,42 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>0.593</v>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/19/2026 8:15:23 AM</t>
+          <t>07/02/2026 11:03:25 AM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>TRUCK 67</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -5041,38 +5037,38 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/18/2026 9:09:41 AM</t>
+          <t>07/01/2026 6:08:17 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5090,38 +5086,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/18/2026 9:00:54 AM</t>
+          <t>07/01/2026 3:07:51 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5139,38 +5135,38 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/18/2026 7:29:06 AM</t>
+          <t>07/01/2026 1:29:57 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5188,38 +5184,38 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/17/2026 12:51:55 PM</t>
+          <t>07/01/2026 12:10:49 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5237,38 +5233,38 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/17/2026 12:24:03 PM</t>
+          <t>07/01/2026 9:29:37 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5276,27 +5272,25 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" t="n">
+        <v>0.708</v>
       </c>
       <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/30/2026 12:19:45 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5311,7 +5305,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5335,32 +5329,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/16/2026 4:15:38 PM</t>
+          <t>06/30/2026 8:20:51 AM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -5374,15 +5368,17 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
-        <v>0.829</v>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/16/2026 1:51:18 PM</t>
+          <t>06/29/2026 1:07:28 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5392,7 +5388,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5407,7 +5403,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -5431,32 +5427,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/15/2026 4:48:21 PM</t>
+          <t>06/29/2026 4:14:57 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -5480,32 +5476,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/12/2026 1:49:28 PM</t>
+          <t>06/26/2026 1:15:05 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -5519,42 +5515,40 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N104" t="n">
+        <v>0.597</v>
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/12/2026 1:29:37 PM</t>
+          <t>06/26/2026 12:30:38 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -5578,38 +5572,38 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/12/2026 12:42:44 PM</t>
+          <t>06/26/2026 11:53:52 AM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5627,38 +5621,38 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51:49 AM</t>
+          <t>06/26/2026 9:29:14 AM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5666,46 +5660,48 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="n">
-        <v>0.775</v>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/12/2026 9:18:27 AM</t>
+          <t>06/25/2026 7:20:50 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5723,32 +5719,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/11/2026 1:13:47 PM</t>
+          <t>06/24/2026 6:03:00 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -5772,27 +5768,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/10/2026 2:13:04 PM</t>
+          <t>06/24/2026 11:16:24 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5803,7 +5799,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5821,38 +5817,38 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/10/2026 12:24:28 PM</t>
+          <t>06/24/2026 10:02:37 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5870,38 +5866,38 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/10/2026 9:43:39 AM</t>
+          <t>06/23/2026 11:23:16 AM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5919,32 +5915,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/10/2026 9:38:39 AM</t>
+          <t>06/20/2026 7:57:27 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -5968,32 +5964,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/10/2026 8:20:12 AM</t>
+          <t>06/19/2026 2:31:31 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -6007,42 +6003,40 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N114" t="n">
+        <v>0.593</v>
       </c>
       <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/10/2026 7:38:13 AM</t>
+          <t>06/19/2026 8:15:23 AM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 202</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Wade DeHaven</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -6056,46 +6050,48 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="n">
-        <v>0.645</v>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/09/2026 5:08:17 PM</t>
+          <t>06/18/2026 9:09:41 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6113,32 +6109,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/08/2026 4:34:35 PM</t>
+          <t>06/18/2026 9:00:54 AM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -6162,32 +6158,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/08/2026 11:36:52 AM</t>
+          <t>06/18/2026 7:29:06 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -6211,38 +6207,38 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/08/2026 8:30:19 AM</t>
+          <t>06/17/2026 12:51:55 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6260,32 +6256,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/05/2026 11:50:44 AM</t>
+          <t>06/17/2026 12:24:03 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>James Townsel</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -6299,40 +6295,42 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="n">
-        <v>0.5649999999999999</v>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/05/2026 10:45:18 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -6356,38 +6354,38 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/05/2026 9:11:54 AM</t>
+          <t>06/16/2026 4:15:38 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6395,48 +6393,46 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N122" t="n">
+        <v>0.829</v>
       </c>
       <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/05/2026 8:11:50 AM</t>
+          <t>06/16/2026 1:51:18 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6454,38 +6450,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/04/2026 4:43:41 PM</t>
+          <t>06/15/2026 4:48:21 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6503,32 +6499,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/04/2026 2:19:48 PM</t>
+          <t>06/12/2026 1:49:28 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -6552,38 +6548,38 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/04/2026 9:36:08 AM</t>
+          <t>06/12/2026 1:29:37 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -6601,32 +6597,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/03/2026 10:39:43 AM</t>
+          <t>06/12/2026 12:42:44 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -6650,38 +6646,38 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/02/2026 8:27:02 PM</t>
+          <t>06/12/2026 10:51:49 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6689,27 +6685,25 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N128" t="n">
+        <v>0.775</v>
       </c>
       <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/02/2026 6:59:41 PM</t>
+          <t>06/12/2026 9:18:27 AM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6724,7 +6718,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -6748,32 +6742,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/02/2026 2:57:58 PM</t>
+          <t>06/11/2026 1:13:47 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -6797,38 +6791,38 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/02/2026 1:08:52 PM</t>
+          <t>06/10/2026 2:13:04 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -6846,38 +6840,38 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/02/2026 12:48:40 PM</t>
+          <t>06/10/2026 12:24:28 PM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6895,12 +6889,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>06/02/2026 11:11:57 AM</t>
+          <t>06/10/2026 9:43:39 AM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6920,7 +6914,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -6944,28 +6938,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>06/01/2026 4:28:39 PM</t>
+          <t>06/10/2026 9:38:39 AM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -6989,32 +6987,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>06/01/2026 12:44:20 PM</t>
+          <t>06/10/2026 8:20:12 AM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -7028,36 +7026,42 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="n">
-        <v>0.516</v>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/29/2026 5:36:46 PM</t>
+          <t>06/10/2026 7:38:13 AM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Randy Fennell</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -7071,44 +7075,46 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N136" t="n">
+        <v>0.645</v>
       </c>
       <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/29/2026 5:35:16 PM</t>
+          <t>06/09/2026 5:08:17 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7126,28 +7132,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>05/29/2026 12:30:16 PM</t>
+          <t>06/08/2026 4:34:35 PM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -7171,28 +7181,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>05/29/2026 10:22:39 AM</t>
+          <t>06/08/2026 11:36:52 AM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Blake Lewis</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -7216,27 +7230,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>05/28/2026 11:10:28 AM</t>
+          <t>06/08/2026 8:30:19 AM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7247,7 +7261,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -7265,32 +7279,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>05/28/2026 7:18:26 AM</t>
+          <t>06/05/2026 11:50:44 AM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>James Townsel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -7304,42 +7318,40 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N141" t="n">
+        <v>0.5649999999999999</v>
       </c>
       <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>05/27/2026 1:48:23 PM</t>
+          <t>06/05/2026 10:45:18 AM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -7353,40 +7365,42 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="n">
-        <v>0.696</v>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>05/27/2026 1:06:15 PM</t>
+          <t>06/05/2026 9:11:54 AM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -7400,40 +7414,42 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="n">
-        <v>0.513</v>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>05/26/2026 1:23:21 PM</t>
+          <t>06/05/2026 8:11:50 AM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -7457,32 +7473,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>05/22/2026 2:52:48 PM</t>
+          <t>06/04/2026 4:43:41 PM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -7506,38 +7522,38 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>05/22/2026 10:07:05 AM</t>
+          <t>06/04/2026 2:19:48 PM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -7555,32 +7571,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>05/22/2026 6:58:39 AM</t>
+          <t>06/04/2026 9:36:08 AM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -7604,32 +7620,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>05/21/2026 5:40:30 PM</t>
+          <t>06/03/2026 10:39:43 AM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -7643,35 +7659,37 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="n">
-        <v>0.636</v>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>05/20/2026 4:28:02 PM</t>
+          <t>06/02/2026 8:27:02 PM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7700,32 +7718,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>05/19/2026 2:01:04 PM</t>
+          <t>06/02/2026 6:59:41 PM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -7749,32 +7767,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>05/19/2026 12:45:47 PM</t>
+          <t>06/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -7788,40 +7806,42 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="n">
-        <v>0.592</v>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>05/18/2026 3:42:24 PM</t>
+          <t>06/02/2026 1:08:52 PM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -7835,46 +7855,48 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="n">
-        <v>0.608</v>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>05/14/2026 4:04:58 PM</t>
+          <t>06/02/2026 12:48:40 PM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -7882,15 +7904,17 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="n">
-        <v>0.541</v>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>05/12/2026 5:09:06 PM</t>
+          <t>06/02/2026 11:11:57 AM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7900,7 +7924,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Miguel Sifuentes</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7921,7 +7945,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -7939,27 +7963,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>05/11/2026 8:03:53 PM</t>
+          <t>06/01/2026 4:28:39 PM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7988,32 +8008,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>05/07/2026 9:29:17 AM</t>
+          <t>06/01/2026 12:44:20 PM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -8027,42 +8047,36 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N156" t="n">
+        <v>0.516</v>
       </c>
       <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>05/06/2026 1:37:47 PM</t>
+          <t>05/29/2026 5:36:46 PM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TRUCK 101</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>John Boerger</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -8076,15 +8090,17 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="n">
-        <v>0.9389999999999999</v>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>05/05/2026 4:49:52 PM</t>
+          <t>05/29/2026 5:35:16 PM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8094,14 +8110,10 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chad Como</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>GEG</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>GEG, PDX</t>
@@ -8109,7 +8121,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -8123,40 +8135,38 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="n">
-        <v>0.508</v>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>05/05/2026 2:55:26 PM</t>
+          <t>05/29/2026 12:30:16 PM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -8180,32 +8190,28 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>05/05/2026 2:01:03 PM</t>
+          <t>05/29/2026 10:22:39 AM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>PDX</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -8219,10 +8225,784 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="n">
-        <v>0.832</v>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>05/28/2026 11:10:28 AM</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Truck 80</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Roy Carney</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Camera Obstruction</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>05/28/2026 7:18:26 AM</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Truck 711</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Shamonte Jacobs</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:48:23 PM</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="O163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:06:15 PM</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="O164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>05/26/2026 1:23:21 PM</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Truck 103</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>John Edmonson</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>05/22/2026 2:52:48 PM</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Truck 704</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>KARVELL OLIVER</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>05/22/2026 10:07:05 AM</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Truck 202</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Wade DeHaven</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BNA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>BNA</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>05/22/2026 6:58:39 AM</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Truck 711</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Charles Smith</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>05/21/2026 5:40:30 PM</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Truck 102</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Andrew Fierro</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="O169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>05/20/2026 4:28:02 PM</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TRUCK 81</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Oscar Hong</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>05/19/2026 2:01:04 PM</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Truck 83</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Jose Hondolero</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>05/19/2026 12:45:47 PM</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Harold Dulaney</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="O172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>05/18/2026 3:42:24 PM</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Truck 102</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Harold Dulaney</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="O173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>05/14/2026 4:04:58 PM</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>truck 706</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Randy Fennell</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Harsh Turn</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="O174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>05/12/2026 5:09:06 PM</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Miguel Sifuentes</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>05/11/2026 8:03:53 PM</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Truck 100</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:O189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/06/2026 9:31:18 PM</t>
+          <t>08/14/2026 4:05:57 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,13 +521,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,38 +545,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/06/2026 4:43:28 PM</t>
+          <t>08/14/2026 9:54:11 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brian Kelly</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -584,35 +584,37 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>0.545</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/06/2026 7:30:46 AM</t>
+          <t>08/14/2026 9:44:41 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -623,7 +625,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -641,7 +643,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/05/2026 6:26:33 PM</t>
+          <t>08/13/2026 3:40:10 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -651,7 +653,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -681,19 +683,19 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.543</v>
+        <v>0.526</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/05/2026 3:11:07 PM</t>
+          <t>08/13/2026 2:02:16 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -737,27 +739,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/05/2026 2:24:40 PM</t>
+          <t>08/13/2026 9:15:16 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -768,7 +770,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -786,32 +788,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/04/2026 3:18:35 PM</t>
+          <t>08/12/2026 4:38:02 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -825,48 +827,46 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>0.508</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/04/2026 9:00:55 AM</t>
+          <t>08/11/2026 3:50:43 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Khali Arrington</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -875,45 +875,45 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0.635</v>
+        <v>0.658</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/03/2026 7:20:40 PM</t>
+          <t>08/11/2026 3:18:05 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -931,38 +931,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/03/2026 6:58:03 PM</t>
+          <t>08/11/2026 12:59:26 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -970,15 +970,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.491</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/03/2026 5:25:29 PM</t>
+          <t>08/11/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1003,7 +1005,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1027,32 +1029,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/03/2026 3:02:06 PM</t>
+          <t>08/10/2026 4:31:38 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1076,27 +1078,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/03/2026 10:53:14 AM</t>
+          <t>08/10/2026 3:59:01 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1107,7 +1109,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1125,17 +1127,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/03/2026 10:05:29 AM</t>
+          <t>08/10/2026 10:15:01 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1150,13 +1152,13 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1174,27 +1176,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/03/2026 9:13:14 AM</t>
+          <t>08/10/2026 9:11:35 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1205,7 +1207,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1223,38 +1225,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/03/2026 8:39:15 AM</t>
+          <t>08/07/2026 8:53:33 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1272,38 +1274,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/31/2026 7:09:03 PM</t>
+          <t>08/06/2026 9:31:18 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kurt Purdie</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1311,46 +1313,48 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0.631</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/31/2026 3:39:46 PM</t>
+          <t>08/06/2026 4:43:28 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Brian Kelly</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1358,42 +1362,40 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N19" t="n">
+        <v>0.545</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/31/2026 3:07:50 PM</t>
+          <t>08/06/2026 7:30:46 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1417,7 +1419,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/31/2026 11:18:13 AM</t>
+          <t>08/06/2026 7:19:47 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,38 +1468,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31/2026 7:03:13 AM</t>
+          <t>08/05/2026 6:26:33 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1505,42 +1507,40 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" t="n">
+        <v>0.543</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/29/2026 2:23:36 PM</t>
+          <t>08/05/2026 3:11:07 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1564,32 +1564,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/29/2026 1:29:51 PM</t>
+          <t>08/05/2026 2:24:40 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1613,27 +1613,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/29/2026 12:50:14 PM</t>
+          <t>08/04/2026 3:18:35 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1662,38 +1662,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/29/2026 10:04:25 AM</t>
+          <t>08/04/2026 9:00:55 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Khali Arrington</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1701,48 +1701,46 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" t="n">
+        <v>0.635</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/28/2026 4:27:30 PM</t>
+          <t>08/03/2026 7:20:40 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1760,32 +1758,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/28/2026 3:53:58 PM</t>
+          <t>08/03/2026 6:58:03 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1799,42 +1797,40 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" t="n">
+        <v>0.491</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/28/2026 3:44:54 PM</t>
+          <t>08/03/2026 5:25:29 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1858,32 +1854,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/28/2026 1:51:55 PM</t>
+          <t>08/03/2026 3:02:06 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1907,38 +1903,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/28/2026 11:42:07 AM</t>
+          <t>08/03/2026 10:53:14 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jerand Townsel</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1956,17 +1952,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/28/2026 11:39:57 AM</t>
+          <t>08/03/2026 10:05:29 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1981,13 +1977,13 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2005,38 +2001,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/28/2026 10:23:00 AM</t>
+          <t>08/03/2026 9:13:14 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2054,7 +2050,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/28/2026 9:57:45 AM</t>
+          <t>08/03/2026 8:39:15 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2079,13 +2075,13 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2103,38 +2099,38 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/28/2026 9:11:05 AM</t>
+          <t>07/31/2026 7:09:03 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Kurt Purdie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2142,42 +2138,40 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N35" t="n">
+        <v>0.631</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/27/2026 5:42:13 PM</t>
+          <t>07/31/2026 3:39:46 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensive Driving, Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2191,46 +2185,48 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>0.529</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/27/2026 2:04:05 PM</t>
+          <t>07/31/2026 3:07:50 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2248,17 +2244,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/27/2026 12:00:04 PM</t>
+          <t>07/31/2026 11:18:13 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2279,7 +2275,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2297,7 +2293,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/27/2026 8:57:57 AM</t>
+          <t>07/31/2026 7:03:13 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2322,13 +2318,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2346,38 +2342,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/24/2026 2:10:44 PM</t>
+          <t>07/29/2026 2:23:36 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2395,32 +2391,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/24/2026 10:45:02 AM</t>
+          <t>07/29/2026 1:29:51 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2444,32 +2440,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24/2026 10:16:36 AM</t>
+          <t>07/29/2026 12:50:14 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2493,32 +2489,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:49 PM</t>
+          <t>07/29/2026 10:04:25 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2542,32 +2538,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/22/2026 5:44:09 PM</t>
+          <t>07/28/2026 4:27:30 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2591,38 +2587,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/21/2026 12:22:30 PM</t>
+          <t>07/28/2026 3:53:58 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TRUCK 85</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>John Boerger</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2640,27 +2636,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/21/2026 12:05:00 PM</t>
+          <t>07/28/2026 3:44:54 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2671,7 +2667,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2689,32 +2685,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/21/2026 11:52:20 AM</t>
+          <t>07/28/2026 1:51:55 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2738,32 +2734,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/20/2026 3:59:36 PM</t>
+          <t>07/28/2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Jerand Townsel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2787,38 +2783,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/16/2026 1:36:56 PM</t>
+          <t>07/28/2026 11:39:57 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2836,32 +2832,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/16/2026 1:17:23 PM</t>
+          <t>07/28/2026 10:23:00 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2885,27 +2881,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15/2026 4:52:33 PM</t>
+          <t>07/28/2026 9:57:45 AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2934,27 +2930,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:43 PM</t>
+          <t>07/28/2026 9:11:05 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2965,7 +2961,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2983,32 +2979,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:25 PM</t>
+          <t>07/27/2026 5:42:13 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Defensive Driving, Harsh Brake</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -3022,27 +3018,25 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N53" t="n">
+        <v>0.529</v>
       </c>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/15/2026 12:15:41 PM</t>
+          <t>07/27/2026 2:04:05 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3057,7 +3051,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3081,27 +3075,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/15/2026 12:10:03 PM</t>
+          <t>07/27/2026 12:00:04 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3112,7 +3106,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3130,7 +3124,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/15/2026 6:28:32 AM</t>
+          <t>07/27/2026 8:57:57 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3140,7 +3134,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3155,7 +3149,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3179,38 +3173,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/14/2026 7:12:18 PM</t>
+          <t>07/24/2026 2:10:44 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3228,27 +3222,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/14/2026 6:10:58 PM</t>
+          <t>07/24/2026 10:45:02 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3277,32 +3271,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/14/2026 5:39:20 PM</t>
+          <t>07/24/2026 10:16:36 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3326,7 +3320,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/14/2026 5:31:40 PM</t>
+          <t>07/22/2026 8:57:49 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3336,7 +3330,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3351,7 +3345,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3375,27 +3369,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/14/2026 11:46:20 AM</t>
+          <t>07/22/2026 5:44:09 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3406,7 +3400,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3424,27 +3418,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/14/2026 9:57:18 AM</t>
+          <t>07/21/2026 12:22:30 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>TRUCK 85</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>John Boerger</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3473,27 +3467,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/14/2026 9:13:03 AM</t>
+          <t>07/21/2026 12:05:00 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>truck 703</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3522,27 +3516,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/13/2026 2:41:35 PM</t>
+          <t>07/21/2026 11:52:20 AM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3553,7 +3547,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3571,38 +3565,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/13/2026 1:03:42 PM</t>
+          <t>07/20/2026 3:59:36 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Juan Santiago</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3620,7 +3614,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/13/2026 12:58:10 PM</t>
+          <t>07/16/2026 1:36:56 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3669,38 +3663,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/13/2026 12:48:08 PM</t>
+          <t>07/16/2026 1:17:23 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3718,7 +3712,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/13/2026 11:24:44 AM</t>
+          <t>07/15/2026 4:52:33 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3743,7 +3737,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3767,38 +3761,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/13/2026 10:27:59 AM</t>
+          <t>07/15/2026 3:06:43 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3816,38 +3810,38 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/12/2026 9:23:11 AM</t>
+          <t>07/15/2026 3:06:25 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OR 70</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3865,27 +3859,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/11/2026 8:35:15 AM</t>
+          <t>07/15/2026 12:15:41 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3896,7 +3890,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3914,27 +3908,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/10/2026 1:09:28 PM</t>
+          <t>07/15/2026 12:10:03 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3945,7 +3939,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3963,7 +3957,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/10/2026 5:25:49 AM</t>
+          <t>07/15/2026 6:28:32 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3973,7 +3967,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3988,7 +3982,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -4012,38 +4006,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/10/2026 4:50:20 AM</t>
+          <t>07/14/2026 7:12:18 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4061,32 +4055,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/09/2026 7:53:06 PM</t>
+          <t>07/14/2026 6:10:58 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -4100,35 +4094,37 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
-        <v>0.671</v>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/09/2026 6:59:54 PM</t>
+          <t>07/14/2026 5:39:20 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4139,7 +4135,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4157,17 +4153,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/09/2026 6:21:15 PM</t>
+          <t>07/14/2026 5:31:40 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4206,38 +4202,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/09/2026 12:47:45 PM</t>
+          <t>07/14/2026 11:46:20 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4255,38 +4251,38 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/09/2026 11:55:07 AM</t>
+          <t>07/14/2026 9:57:18 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4304,32 +4300,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/08/2026 6:29:26 PM</t>
+          <t>07/14/2026 9:13:03 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>truck 703</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -4353,27 +4349,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/08/2026 11:40:54 AM</t>
+          <t>07/13/2026 2:41:35 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truck 803</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4402,32 +4398,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/08/2026 10:12:05 AM</t>
+          <t>07/13/2026 1:03:42 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Juan Santiago</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4451,27 +4447,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/07/2026 8:03:23 PM</t>
+          <t>07/13/2026 12:58:10 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4482,7 +4478,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4500,27 +4496,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/07/2026 6:38:32 PM</t>
+          <t>07/13/2026 12:48:08 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4531,7 +4527,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4549,32 +4545,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/07/2026 2:48:19 PM</t>
+          <t>07/13/2026 11:24:44 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4598,38 +4594,38 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/06/2026 10:26:03 PM</t>
+          <t>07/13/2026 10:27:59 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4647,32 +4643,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/06/2026 7:14:26 AM</t>
+          <t>07/12/2026 9:23:11 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4696,32 +4692,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/02/2026 5:15:10 PM</t>
+          <t>07/11/2026 8:35:15 AM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -4745,27 +4741,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/02/2026 1:50:55 PM</t>
+          <t>07/10/2026 1:09:28 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4776,7 +4772,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4794,17 +4790,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/02/2026 12:25:36 PM</t>
+          <t>07/10/2026 5:25:49 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4843,38 +4839,38 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/02/2026 12:22:00 PM</t>
+          <t>07/10/2026 4:50:20 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4892,27 +4888,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/02/2026 12:00:30 PM</t>
+          <t>07/09/2026 7:53:06 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4932,34 +4928,34 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>0.534</v>
+        <v>0.671</v>
       </c>
       <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/02/2026 11:56:44 AM</t>
+          <t>07/09/2026 6:59:54 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4988,27 +4984,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/02/2026 11:03:25 AM</t>
+          <t>07/09/2026 6:21:15 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TRUCK 67</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5037,38 +5033,38 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/01/2026 6:08:17 PM</t>
+          <t>07/09/2026 12:47:45 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5086,27 +5082,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/01/2026 3:07:51 PM</t>
+          <t>07/09/2026 11:55:07 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5135,38 +5131,38 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/01/2026 1:29:57 PM</t>
+          <t>07/08/2026 6:29:26 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5184,27 +5180,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/01/2026 12:10:49 PM</t>
+          <t>07/08/2026 11:40:54 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 803</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5233,17 +5229,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/01/2026 9:29:37 AM</t>
+          <t>07/08/2026 10:12:05 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5258,7 +5254,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -5272,25 +5268,27 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
-        <v>0.708</v>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/30/2026 12:19:45 PM</t>
+          <t>07/07/2026 8:03:23 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5305,7 +5303,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5329,38 +5327,38 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/30/2026 8:20:51 AM</t>
+          <t>07/07/2026 6:38:32 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5378,38 +5376,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/29/2026 1:07:28 PM</t>
+          <t>07/07/2026 2:48:19 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5427,38 +5425,38 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/29/2026 4:14:57 AM</t>
+          <t>07/06/2026 10:26:03 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5476,32 +5474,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/26/2026 1:15:05 PM</t>
+          <t>07/06/2026 7:14:26 AM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -5515,46 +5513,48 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="n">
-        <v>0.597</v>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/26/2026 12:30:38 PM</t>
+          <t>07/02/2026 5:15:10 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5572,38 +5572,38 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/26/2026 11:53:52 AM</t>
+          <t>07/02/2026 1:50:55 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5621,38 +5621,38 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/26/2026 9:29:14 AM</t>
+          <t>07/02/2026 12:25:36 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5670,38 +5670,38 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/25/2026 7:20:50 PM</t>
+          <t>07/02/2026 12:22:00 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5719,32 +5719,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/24/2026 6:03:00 PM</t>
+          <t>07/02/2026 12:00:30 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -5758,48 +5758,46 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N109" t="n">
+        <v>0.534</v>
       </c>
       <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/24/2026 11:16:24 AM</t>
+          <t>07/02/2026 11:56:44 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5817,38 +5815,38 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/24/2026 10:02:37 AM</t>
+          <t>07/02/2026 11:03:25 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 67</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5866,32 +5864,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/23/2026 11:23:16 AM</t>
+          <t>07/01/2026 6:08:17 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -5915,38 +5913,38 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/20/2026 7:57:27 PM</t>
+          <t>07/01/2026 3:07:51 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5964,38 +5962,38 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/19/2026 2:31:31 PM</t>
+          <t>07/01/2026 1:29:57 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6003,46 +6001,48 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="n">
-        <v>0.593</v>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/19/2026 8:15:23 AM</t>
+          <t>07/01/2026 12:10:49 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6060,38 +6060,38 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/18/2026 9:09:41 AM</t>
+          <t>07/01/2026 9:29:37 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6099,42 +6099,40 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N116" t="n">
+        <v>0.708</v>
       </c>
       <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/18/2026 9:00:54 AM</t>
+          <t>06/30/2026 12:19:45 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -6158,38 +6156,38 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/18/2026 7:29:06 AM</t>
+          <t>06/30/2026 8:20:51 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6207,38 +6205,38 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/17/2026 12:51:55 PM</t>
+          <t>06/29/2026 1:07:28 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6256,38 +6254,38 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/17/2026 12:24:03 PM</t>
+          <t>06/29/2026 4:14:57 AM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6305,38 +6303,38 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/26/2026 1:15:05 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6344,42 +6342,40 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N121" t="n">
+        <v>0.597</v>
       </c>
       <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/16/2026 4:15:38 PM</t>
+          <t>06/26/2026 12:30:38 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -6393,15 +6389,17 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="n">
-        <v>0.829</v>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/16/2026 1:51:18 PM</t>
+          <t>06/26/2026 11:53:52 AM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6411,7 +6409,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6426,7 +6424,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -6450,38 +6448,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/15/2026 4:48:21 PM</t>
+          <t>06/26/2026 9:29:14 AM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6499,17 +6497,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/12/2026 1:49:28 PM</t>
+          <t>06/25/2026 7:20:50 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6524,7 +6522,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -6548,27 +6546,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/12/2026 1:29:37 PM</t>
+          <t>06/24/2026 6:03:00 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6579,7 +6577,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -6597,32 +6595,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/12/2026 12:42:44 PM</t>
+          <t>06/24/2026 11:16:24 AM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -6646,7 +6644,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51:49 AM</t>
+          <t>06/24/2026 10:02:37 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6671,7 +6669,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -6685,46 +6683,48 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="n">
-        <v>0.775</v>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/12/2026 9:18:27 AM</t>
+          <t>06/23/2026 11:23:16 AM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/11/2026 1:13:47 PM</t>
+          <t>06/20/2026 7:57:27 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -6791,38 +6791,38 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/10/2026 2:13:04 PM</t>
+          <t>06/19/2026 2:31:31 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -6830,42 +6830,40 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N131" t="n">
+        <v>0.593</v>
       </c>
       <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/10/2026 12:24:28 PM</t>
+          <t>06/19/2026 8:15:23 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 202</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Wade DeHaven</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -6889,32 +6887,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>06/10/2026 9:43:39 AM</t>
+          <t>06/18/2026 9:09:41 AM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -6938,32 +6936,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>06/10/2026 9:38:39 AM</t>
+          <t>06/18/2026 9:00:54 AM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -6987,27 +6985,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>06/10/2026 8:20:12 AM</t>
+          <t>06/18/2026 7:29:06 AM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7036,12 +7034,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06/10/2026 7:38:13 AM</t>
+          <t>06/17/2026 12:51:55 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7061,7 +7059,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -7075,46 +7073,48 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="n">
-        <v>0.645</v>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>06/09/2026 5:08:17 PM</t>
+          <t>06/17/2026 12:24:03 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7132,32 +7132,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>06/08/2026 4:34:35 PM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -7181,38 +7181,38 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>06/08/2026 11:36:52 AM</t>
+          <t>06/16/2026 4:15:38 PM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7220,42 +7220,40 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N139" t="n">
+        <v>0.829</v>
       </c>
       <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>06/08/2026 8:30:19 AM</t>
+          <t>06/16/2026 1:51:18 PM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -7279,38 +7277,38 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>06/05/2026 11:50:44 AM</t>
+          <t>06/15/2026 4:48:21 PM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>James Townsel</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -7318,46 +7316,48 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="n">
-        <v>0.5649999999999999</v>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>06/05/2026 10:45:18 AM</t>
+          <t>06/12/2026 1:49:28 PM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7375,38 +7375,38 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>06/05/2026 9:11:54 AM</t>
+          <t>06/12/2026 1:29:37 PM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7424,32 +7424,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>06/05/2026 8:11:50 AM</t>
+          <t>06/12/2026 12:42:44 PM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -7473,38 +7473,38 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>06/04/2026 4:43:41 PM</t>
+          <t>06/12/2026 10:51:49 AM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -7512,48 +7512,46 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N145" t="n">
+        <v>0.775</v>
       </c>
       <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>06/04/2026 2:19:48 PM</t>
+          <t>06/12/2026 9:18:27 AM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -7571,32 +7569,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>06/04/2026 9:36:08 AM</t>
+          <t>06/11/2026 1:13:47 PM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -7620,38 +7618,38 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>06/03/2026 10:39:43 AM</t>
+          <t>06/10/2026 2:13:04 PM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -7669,7 +7667,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06/02/2026 8:27:02 PM</t>
+          <t>06/10/2026 12:24:28 PM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7718,32 +7716,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06/02/2026 6:59:41 PM</t>
+          <t>06/10/2026 9:43:39 AM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -7767,32 +7765,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>06/02/2026 2:57:58 PM</t>
+          <t>06/10/2026 9:38:39 AM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -7816,32 +7814,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>06/02/2026 1:08:52 PM</t>
+          <t>06/10/2026 8:20:12 AM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -7865,38 +7863,38 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>06/02/2026 12:48:40 PM</t>
+          <t>06/10/2026 7:38:13 AM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -7904,22 +7902,20 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N153" t="n">
+        <v>0.645</v>
       </c>
       <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>06/02/2026 11:11:57 AM</t>
+          <t>06/09/2026 5:08:17 PM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7939,13 +7935,13 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -7963,23 +7959,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>06/01/2026 4:28:39 PM</t>
+          <t>06/08/2026 4:34:35 PM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8008,32 +8008,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>06/01/2026 12:44:20 PM</t>
+          <t>06/08/2026 11:36:52 AM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -8047,42 +8047,48 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="n">
-        <v>0.516</v>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>05/29/2026 5:36:46 PM</t>
+          <t>06/08/2026 8:30:19 AM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Michael Reynoso</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -8100,28 +8106,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>05/29/2026 5:35:16 PM</t>
+          <t>06/05/2026 11:50:44 AM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>James Townsel</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -8135,38 +8145,40 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N158" t="n">
+        <v>0.5649999999999999</v>
       </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>05/29/2026 12:30:16 PM</t>
+          <t>06/05/2026 10:45:18 AM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Jose Hondolero</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -8190,28 +8202,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>05/29/2026 10:22:39 AM</t>
+          <t>06/05/2026 9:11:54 AM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -8235,27 +8251,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>05/28/2026 11:10:28 AM</t>
+          <t>06/05/2026 8:11:50 AM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8284,32 +8300,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>05/28/2026 7:18:26 AM</t>
+          <t>06/04/2026 4:43:41 PM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -8333,38 +8349,38 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>05/27/2026 1:48:23 PM</t>
+          <t>06/04/2026 2:19:48 PM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -8372,40 +8388,42 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="n">
-        <v>0.696</v>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>05/27/2026 1:06:15 PM</t>
+          <t>06/04/2026 9:36:08 AM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -8419,40 +8437,42 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="n">
-        <v>0.513</v>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>05/26/2026 1:23:21 PM</t>
+          <t>06/03/2026 10:39:43 AM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -8476,27 +8496,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>05/22/2026 2:52:48 PM</t>
+          <t>06/02/2026 8:27:02 PM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8525,32 +8545,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>05/22/2026 10:07:05 AM</t>
+          <t>06/02/2026 6:59:41 PM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -8574,32 +8594,32 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>05/22/2026 6:58:39 AM</t>
+          <t>06/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
@@ -8623,32 +8643,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>05/21/2026 5:40:30 PM</t>
+          <t>06/02/2026 1:08:52 PM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
@@ -8662,46 +8682,48 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="n">
-        <v>0.636</v>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>05/20/2026 4:28:02 PM</t>
+          <t>06/02/2026 12:48:40 PM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -8719,27 +8741,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>05/19/2026 2:01:04 PM</t>
+          <t>06/02/2026 11:11:57 AM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 75</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8768,32 +8790,28 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>05/19/2026 12:45:47 PM</t>
+          <t>06/01/2026 4:28:39 PM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>PDX</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -8807,40 +8825,42 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="n">
-        <v>0.592</v>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>05/18/2026 3:42:24 PM</t>
+          <t>06/01/2026 12:44:20 PM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -8855,39 +8875,35 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
-        <v>0.608</v>
+        <v>0.516</v>
       </c>
       <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>05/14/2026 4:04:58 PM</t>
+          <t>05/29/2026 5:36:46 PM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G174" t="inlineStr"/>
@@ -8901,46 +8917,44 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="n">
-        <v>0.541</v>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>05/12/2026 5:09:06 PM</t>
+          <t>05/29/2026 5:35:16 PM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miguel Sifuentes</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -8958,32 +8972,28 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>05/11/2026 8:03:53 PM</t>
+          <t>05/29/2026 12:30:16 PM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -9004,6 +9014,631 @@
       </c>
       <c r="O176" t="inlineStr"/>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>05/29/2026 10:22:39 AM</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Truck 800</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>GEG, PDX</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>05/28/2026 11:10:28 AM</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Truck 80</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Roy Carney</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Camera Obstruction</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>05/28/2026 7:18:26 AM</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Truck 711</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Shamonte Jacobs</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:48:23 PM</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="O180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:06:15 PM</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="O181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>05/26/2026 1:23:21 PM</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Truck 103</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>John Edmonson</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>05/22/2026 2:52:48 PM</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Truck 704</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>KARVELL OLIVER</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>05/22/2026 10:07:05 AM</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Truck 202</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Wade DeHaven</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BNA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>BNA</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>05/22/2026 6:58:39 AM</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Truck 711</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Charles Smith</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>05/21/2026 5:40:30 PM</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Truck 102</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Andrew Fierro</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="O186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>05/20/2026 4:28:02 PM</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TRUCK 81</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Oscar Hong</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>05/19/2026 2:01:04 PM</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Truck 83</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Jose Hondolero</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>05/19/2026 12:45:47 PM</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Harold Dulaney</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>PDX</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="O189" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O189"/>
+  <dimension ref="A1:O193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,38 +496,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/14/2026 4:05:57 PM</t>
+          <t>08/20/2026 2:10:00 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,27 +545,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/14/2026 9:54:11 AM</t>
+          <t>08/20/2026 12:19:12 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -576,7 +576,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,27 +594,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/14/2026 9:44:41 AM</t>
+          <t>08/19/2026 12:36:10 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,7 +625,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -643,32 +643,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/13/2026 3:40:10 PM</t>
+          <t>08/19/2026 11:30:26 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -682,40 +682,42 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>0.526</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/13/2026 2:02:16 PM</t>
+          <t>08/18/2026 9:06:54 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -739,7 +741,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/13/2026 9:15:16 AM</t>
+          <t>08/18/2026 9:27:08 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -749,7 +751,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -770,7 +772,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -788,32 +790,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/12/2026 4:38:02 PM</t>
+          <t>08/18/2026 8:29:18 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -827,40 +829,42 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.508</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/11/2026 3:50:43 PM</t>
+          <t>08/17/2026 2:27:02 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -874,40 +878,42 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.658</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/11/2026 3:18:05 PM</t>
+          <t>08/17/2026 12:11:17 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -931,32 +937,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/11/2026 12:59:26 PM</t>
+          <t>08/17/2026 10:13:40 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -970,42 +976,40 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N11" t="n">
+        <v>0.509</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/11/2026 9:49:26 AM</t>
+          <t>08/17/2026 8:30:21 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1029,17 +1033,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/10/2026 4:31:38 PM</t>
+          <t>08/14/2026 4:05:57 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1054,7 +1058,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1078,27 +1082,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/10/2026 3:59:01 PM</t>
+          <t>08/14/2026 9:54:11 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1127,32 +1131,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/10/2026 10:15:01 AM</t>
+          <t>08/14/2026 9:44:41 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1176,32 +1180,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/10/2026 9:11:35 AM</t>
+          <t>08/13/2026 3:40:10 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1215,42 +1219,40 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" t="n">
+        <v>0.526</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/07/2026 8:53:33 AM</t>
+          <t>08/13/2026 2:02:16 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1274,38 +1276,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/06/2026 9:31:18 PM</t>
+          <t>08/13/2026 9:15:16 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1323,27 +1325,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/06/2026 4:43:28 PM</t>
+          <t>08/12/2026 4:38:02 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brian Kelly</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1363,39 +1365,39 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>0.545</v>
+        <v>0.508</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/06/2026 7:30:46 AM</t>
+          <t>08/11/2026 3:50:43 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1409,42 +1411,40 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>0.658</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/06/2026 7:19:47 AM</t>
+          <t>08/11/2026 3:18:05 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1468,38 +1468,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/05/2026 6:26:33 PM</t>
+          <t>08/11/2026 12:59:26 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1507,40 +1507,42 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>0.543</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/05/2026 3:11:07 PM</t>
+          <t>08/11/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1564,32 +1566,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/05/2026 2:24:40 PM</t>
+          <t>08/10/2026 4:31:38 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1613,32 +1615,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/04/2026 3:18:35 PM</t>
+          <t>08/10/2026 3:59:01 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1662,17 +1664,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/04/2026 9:00:55 AM</t>
+          <t>08/10/2026 10:15:01 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Khali Arrington</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1687,13 +1689,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1701,46 +1703,48 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>0.635</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/03/2026 7:20:40 PM</t>
+          <t>08/10/2026 9:11:35 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1758,38 +1762,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/03/2026 6:58:03 PM</t>
+          <t>08/07/2026 8:53:33 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1797,25 +1801,27 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0.491</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/03/2026 5:25:29 PM</t>
+          <t>08/06/2026 9:31:18 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1830,7 +1836,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1854,38 +1860,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/03/2026 3:02:06 PM</t>
+          <t>08/06/2026 4:43:28 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Brian Kelly</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1893,37 +1899,35 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N30" t="n">
+        <v>0.545</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/03/2026 10:53:14 AM</t>
+          <t>08/06/2026 7:30:46 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1934,7 +1938,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1952,27 +1956,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/03/2026 10:05:29 AM</t>
+          <t>08/06/2026 7:19:47 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1983,7 +1987,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2001,32 +2005,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/03/2026 9:13:14 AM</t>
+          <t>08/05/2026 6:26:33 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2040,42 +2044,40 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N33" t="n">
+        <v>0.543</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/03/2026 8:39:15 AM</t>
+          <t>08/05/2026 3:11:07 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2099,17 +2101,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/31/2026 7:09:03 PM</t>
+          <t>08/05/2026 2:24:40 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kurt Purdie</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2124,7 +2126,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2138,40 +2140,42 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>0.631</v>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/31/2026 3:39:46 PM</t>
+          <t>08/04/2026 3:18:35 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2195,38 +2199,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/31/2026 3:07:50 PM</t>
+          <t>08/04/2026 9:00:55 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Khali Arrington</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2234,48 +2238,46 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N37" t="n">
+        <v>0.635</v>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/31/2026 11:18:13 AM</t>
+          <t>08/03/2026 7:20:40 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2293,38 +2295,38 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/31/2026 7:03:13 AM</t>
+          <t>08/03/2026 6:58:03 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2332,42 +2334,40 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N39" t="n">
+        <v>0.491</v>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/29/2026 2:23:36 PM</t>
+          <t>08/03/2026 5:25:29 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2391,27 +2391,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/29/2026 1:29:51 PM</t>
+          <t>08/03/2026 3:02:06 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2440,17 +2440,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/29/2026 12:50:14 PM</t>
+          <t>08/03/2026 10:53:14 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2465,13 +2465,13 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2489,27 +2489,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/29/2026 10:04:25 AM</t>
+          <t>08/03/2026 10:05:29 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2520,7 +2520,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2538,17 +2538,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/28/2026 4:27:30 PM</t>
+          <t>08/03/2026 9:13:14 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2563,13 +2563,13 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2587,38 +2587,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/28/2026 3:53:58 PM</t>
+          <t>08/03/2026 8:39:15 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2636,32 +2636,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/28/2026 3:44:54 PM</t>
+          <t>07/31/2026 7:09:03 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Kurt Purdie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2675,37 +2675,35 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N46" t="n">
+        <v>0.631</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/28/2026 1:51:55 PM</t>
+          <t>07/31/2026 3:39:46 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2734,7 +2732,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/28/2026 11:42:07 AM</t>
+          <t>07/31/2026 3:07:50 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2744,7 +2742,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jerand Townsel</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2759,7 +2757,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2783,32 +2781,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/28/2026 11:39:57 AM</t>
+          <t>07/31/2026 11:18:13 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2832,17 +2830,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/28/2026 10:23:00 AM</t>
+          <t>07/31/2026 7:03:13 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2857,7 +2855,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2881,32 +2879,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/28/2026 9:57:45 AM</t>
+          <t>07/29/2026 2:23:36 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2930,32 +2928,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/28/2026 9:11:05 AM</t>
+          <t>07/29/2026 1:29:51 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2979,32 +2977,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/27/2026 5:42:13 PM</t>
+          <t>07/29/2026 12:50:14 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Defensive Driving, Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -3018,46 +3016,48 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>0.529</v>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/27/2026 2:04:05 PM</t>
+          <t>07/29/2026 10:04:25 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3075,38 +3075,38 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/27/2026 12:00:04 PM</t>
+          <t>07/28/2026 4:27:30 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3124,17 +3124,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/27/2026 8:57:57 AM</t>
+          <t>07/28/2026 3:53:58 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3173,27 +3173,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/24/2026 2:10:44 PM</t>
+          <t>07/28/2026 3:44:54 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3204,7 +3204,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3222,32 +3222,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/24/2026 10:45:02 AM</t>
+          <t>07/28/2026 1:51:55 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3271,32 +3271,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/24/2026 10:16:36 AM</t>
+          <t>07/28/2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Jerand Townsel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3320,32 +3320,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:49 PM</t>
+          <t>07/28/2026 11:39:57 AM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3369,32 +3369,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/22/2026 5:44:09 PM</t>
+          <t>07/28/2026 10:23:00 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3418,32 +3418,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/21/2026 12:22:30 PM</t>
+          <t>07/28/2026 9:57:45 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TRUCK 85</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>John Boerger</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/21/2026 12:05:00 PM</t>
+          <t>07/28/2026 9:11:05 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3498,7 +3498,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3516,32 +3516,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/21/2026 11:52:20 AM</t>
+          <t>07/27/2026 5:42:13 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Defensive Driving, Harsh Brake</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3555,48 +3555,46 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N64" t="n">
+        <v>0.529</v>
       </c>
       <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/20/2026 3:59:36 PM</t>
+          <t>07/27/2026 2:04:05 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3614,7 +3612,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/16/2026 1:36:56 PM</t>
+          <t>07/27/2026 12:00:04 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3624,7 +3622,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3663,38 +3661,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/16/2026 1:17:23 PM</t>
+          <t>07/27/2026 8:57:57 AM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3712,27 +3710,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/15/2026 4:52:33 PM</t>
+          <t>07/24/2026 2:10:44 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3743,7 +3741,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3761,7 +3759,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:43 PM</t>
+          <t>07/24/2026 10:45:02 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3771,7 +3769,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3810,32 +3808,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:25 PM</t>
+          <t>07/24/2026 10:16:36 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3859,38 +3857,38 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/15/2026 12:15:41 PM</t>
+          <t>07/22/2026 8:57:49 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3908,12 +3906,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/15/2026 12:10:03 PM</t>
+          <t>07/22/2026 5:44:09 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3957,38 +3955,38 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/15/2026 6:28:32 AM</t>
+          <t>07/21/2026 12:22:30 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 85</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>John Boerger</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4006,38 +4004,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/14/2026 7:12:18 PM</t>
+          <t>07/21/2026 12:05:00 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4055,27 +4053,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/14/2026 6:10:58 PM</t>
+          <t>07/21/2026 11:52:20 AM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4104,7 +4102,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/14/2026 5:39:20 PM</t>
+          <t>07/20/2026 3:59:36 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4114,7 +4112,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4129,7 +4127,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4153,27 +4151,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/14/2026 5:31:40 PM</t>
+          <t>07/16/2026 1:36:56 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4184,7 +4182,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4202,38 +4200,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/14/2026 11:46:20 AM</t>
+          <t>07/16/2026 1:17:23 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4251,32 +4249,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/14/2026 9:57:18 AM</t>
+          <t>07/15/2026 4:52:33 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4300,12 +4298,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/14/2026 9:13:03 AM</t>
+          <t>07/15/2026 3:06:43 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>truck 703</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4349,38 +4347,38 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/13/2026 2:41:35 PM</t>
+          <t>07/15/2026 3:06:25 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4398,32 +4396,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/13/2026 1:03:42 PM</t>
+          <t>07/15/2026 12:15:41 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Juan Santiago</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4447,27 +4445,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/13/2026 12:58:10 PM</t>
+          <t>07/15/2026 12:10:03 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4478,7 +4476,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4496,7 +4494,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/13/2026 12:48:08 PM</t>
+          <t>07/15/2026 6:28:32 AM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4506,7 +4504,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4521,7 +4519,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -4545,32 +4543,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/13/2026 11:24:44 AM</t>
+          <t>07/14/2026 7:12:18 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4594,38 +4592,38 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/13/2026 10:27:59 AM</t>
+          <t>07/14/2026 6:10:58 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4643,38 +4641,38 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/12/2026 9:23:11 AM</t>
+          <t>07/14/2026 5:39:20 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OR 70</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4692,27 +4690,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/11/2026 8:35:15 AM</t>
+          <t>07/14/2026 5:31:40 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4741,27 +4739,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/10/2026 1:09:28 PM</t>
+          <t>07/14/2026 11:46:20 AM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4790,38 +4788,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/10/2026 5:25:49 AM</t>
+          <t>07/14/2026 9:57:18 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4839,38 +4837,38 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/10/2026 4:50:20 AM</t>
+          <t>07/14/2026 9:13:03 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>truck 703</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4888,38 +4886,38 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/09/2026 7:53:06 PM</t>
+          <t>07/13/2026 2:41:35 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4927,25 +4925,27 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
-        <v>0.671</v>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/09/2026 6:59:54 PM</t>
+          <t>07/13/2026 1:03:42 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Juan Santiago</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -4984,27 +4984,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/09/2026 6:21:15 PM</t>
+          <t>07/13/2026 12:58:10 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5015,7 +5015,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5033,38 +5033,38 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/09/2026 12:47:45 PM</t>
+          <t>07/13/2026 12:48:08 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5082,38 +5082,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/09/2026 11:55:07 AM</t>
+          <t>07/13/2026 11:24:44 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5131,38 +5131,38 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/08/2026 6:29:26 PM</t>
+          <t>07/13/2026 10:27:59 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5180,32 +5180,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/08/2026 11:40:54 AM</t>
+          <t>07/12/2026 9:23:11 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Truck 803</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5229,27 +5229,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/08/2026 10:12:05 AM</t>
+          <t>07/11/2026 8:35:15 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5260,7 +5260,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5278,27 +5278,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/07/2026 8:03:23 PM</t>
+          <t>07/10/2026 1:09:28 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5309,7 +5309,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5327,27 +5327,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/07/2026 6:38:32 PM</t>
+          <t>07/10/2026 5:25:49 AM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5358,7 +5358,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5376,38 +5376,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/07/2026 2:48:19 PM</t>
+          <t>07/10/2026 4:50:20 AM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5425,32 +5425,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>07/06/2026 10:26:03 PM</t>
+          <t>07/09/2026 7:53:06 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -5464,37 +5464,35 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N103" t="n">
+        <v>0.671</v>
       </c>
       <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>07/06/2026 7:14:26 AM</t>
+          <t>07/09/2026 6:59:54 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5523,32 +5521,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>07/02/2026 5:15:10 PM</t>
+          <t>07/09/2026 6:21:15 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -5572,32 +5570,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>07/02/2026 1:50:55 PM</t>
+          <t>07/09/2026 12:47:45 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -5621,7 +5619,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>07/02/2026 12:25:36 PM</t>
+          <t>07/09/2026 11:55:07 AM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5670,32 +5668,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>07/02/2026 12:22:00 PM</t>
+          <t>07/08/2026 6:29:26 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -5719,38 +5717,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07/02/2026 12:00:30 PM</t>
+          <t>07/08/2026 11:40:54 AM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 803</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5758,25 +5756,27 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="n">
-        <v>0.534</v>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>07/02/2026 11:56:44 AM</t>
+          <t>07/08/2026 10:12:05 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5815,27 +5815,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07/02/2026 11:03:25 AM</t>
+          <t>07/07/2026 8:03:23 PM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TRUCK 67</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5864,27 +5864,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07/01/2026 6:08:17 PM</t>
+          <t>07/07/2026 6:38:32 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5895,7 +5895,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5913,38 +5913,38 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07/01/2026 3:07:51 PM</t>
+          <t>07/07/2026 2:48:19 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5962,27 +5962,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07/01/2026 1:29:57 PM</t>
+          <t>07/06/2026 10:26:03 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5993,7 +5993,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07/01/2026 12:10:49 PM</t>
+          <t>07/06/2026 7:14:26 AM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6060,38 +6060,38 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07/01/2026 9:29:37 AM</t>
+          <t>07/02/2026 5:15:10 PM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6099,40 +6099,42 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="n">
-        <v>0.708</v>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/30/2026 12:19:45 PM</t>
+          <t>07/02/2026 1:50:55 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -6156,17 +6158,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/30/2026 8:20:51 AM</t>
+          <t>07/02/2026 12:25:36 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6181,7 +6183,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -6205,27 +6207,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/29/2026 1:07:28 PM</t>
+          <t>07/02/2026 12:22:00 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6236,7 +6238,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6254,38 +6256,38 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/29/2026 4:14:57 AM</t>
+          <t>07/02/2026 12:00:30 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6293,42 +6295,40 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N120" t="n">
+        <v>0.534</v>
       </c>
       <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/26/2026 1:15:05 PM</t>
+          <t>07/02/2026 11:56:44 AM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -6342,46 +6342,48 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
-        <v>0.597</v>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/26/2026 12:30:38 PM</t>
+          <t>07/02/2026 11:03:25 AM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 67</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6399,32 +6401,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/26/2026 11:53:52 AM</t>
+          <t>07/01/2026 6:08:17 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -6448,38 +6450,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/26/2026 9:29:14 AM</t>
+          <t>07/01/2026 3:07:51 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6497,32 +6499,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/25/2026 7:20:50 PM</t>
+          <t>07/01/2026 1:29:57 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -6546,38 +6548,38 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/24/2026 6:03:00 PM</t>
+          <t>07/01/2026 12:10:49 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -6595,38 +6597,38 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/24/2026 11:16:24 AM</t>
+          <t>07/01/2026 9:29:37 AM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6634,48 +6636,46 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N127" t="n">
+        <v>0.708</v>
       </c>
       <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/24/2026 10:02:37 AM</t>
+          <t>06/30/2026 12:19:45 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6693,17 +6693,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/23/2026 11:23:16 AM</t>
+          <t>06/30/2026 8:20:51 AM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6742,38 +6742,38 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/20/2026 7:57:27 PM</t>
+          <t>06/29/2026 1:07:28 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -6791,38 +6791,38 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/19/2026 2:31:31 PM</t>
+          <t>06/29/2026 4:14:57 AM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -6830,46 +6830,48 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="n">
-        <v>0.593</v>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/19/2026 8:15:23 AM</t>
+          <t>06/26/2026 1:15:05 PM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6877,37 +6879,35 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N132" t="n">
+        <v>0.597</v>
       </c>
       <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>06/18/2026 9:09:41 AM</t>
+          <t>06/26/2026 12:30:38 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6918,7 +6918,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -6936,27 +6936,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>06/18/2026 9:00:54 AM</t>
+          <t>06/26/2026 11:53:52 AM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -6985,32 +6985,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>06/18/2026 7:29:06 AM</t>
+          <t>06/26/2026 9:29:14 AM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -7034,38 +7034,38 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06/17/2026 12:51:55 PM</t>
+          <t>06/25/2026 7:20:50 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -7083,32 +7083,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>06/17/2026 12:24:03 PM</t>
+          <t>06/24/2026 6:03:00 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -7132,17 +7132,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/24/2026 11:16:24 AM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -7181,32 +7181,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>06/16/2026 4:15:38 PM</t>
+          <t>06/24/2026 10:02:37 AM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -7220,15 +7220,17 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="n">
-        <v>0.829</v>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>06/16/2026 1:51:18 PM</t>
+          <t>06/23/2026 11:23:16 AM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7238,7 +7240,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7277,38 +7279,38 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>06/15/2026 4:48:21 PM</t>
+          <t>06/20/2026 7:57:27 PM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -7326,38 +7328,38 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>06/12/2026 1:49:28 PM</t>
+          <t>06/19/2026 2:31:31 PM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7365,37 +7367,35 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N142" t="n">
+        <v>0.593</v>
       </c>
       <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>06/12/2026 1:29:37 PM</t>
+          <t>06/19/2026 8:15:23 AM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 202</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Wade DeHaven</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7406,7 +7406,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7424,32 +7424,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>06/12/2026 12:42:44 PM</t>
+          <t>06/18/2026 9:09:41 AM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -7473,38 +7473,38 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51:49 AM</t>
+          <t>06/18/2026 9:00:54 AM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -7512,40 +7512,42 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="n">
-        <v>0.775</v>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>06/12/2026 9:18:27 AM</t>
+          <t>06/18/2026 7:29:06 AM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -7569,32 +7571,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>06/11/2026 1:13:47 PM</t>
+          <t>06/17/2026 12:51:55 PM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -7618,38 +7620,38 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>06/10/2026 2:13:04 PM</t>
+          <t>06/17/2026 12:24:03 PM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -7667,7 +7669,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06/10/2026 12:24:28 PM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7692,7 +7694,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -7716,38 +7718,38 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06/10/2026 9:43:39 AM</t>
+          <t>06/16/2026 4:15:38 PM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -7755,48 +7757,46 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N150" t="n">
+        <v>0.829</v>
       </c>
       <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>06/10/2026 9:38:39 AM</t>
+          <t>06/16/2026 1:51:18 PM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -7814,27 +7814,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>06/10/2026 8:20:12 AM</t>
+          <t>06/15/2026 4:48:21 PM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7863,38 +7863,38 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>06/10/2026 7:38:13 AM</t>
+          <t>06/12/2026 1:49:28 PM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -7902,40 +7902,42 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="n">
-        <v>0.645</v>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>06/09/2026 5:08:17 PM</t>
+          <t>06/12/2026 1:29:37 PM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -7959,32 +7961,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>06/08/2026 4:34:35 PM</t>
+          <t>06/12/2026 12:42:44 PM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -8008,38 +8010,38 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>06/08/2026 11:36:52 AM</t>
+          <t>06/12/2026 10:51:49 AM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -8047,17 +8049,15 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N156" t="n">
+        <v>0.775</v>
       </c>
       <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>06/08/2026 8:30:19 AM</t>
+          <t>06/12/2026 9:18:27 AM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8088,7 +8088,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -8106,32 +8106,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>06/05/2026 11:50:44 AM</t>
+          <t>06/11/2026 1:13:47 PM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>James Townsel</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -8145,35 +8145,37 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="n">
-        <v>0.5649999999999999</v>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>06/05/2026 10:45:18 AM</t>
+          <t>06/10/2026 2:13:04 PM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8184,7 +8186,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -8202,12 +8204,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>06/05/2026 9:11:54 AM</t>
+          <t>06/10/2026 12:24:28 PM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8227,7 +8229,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -8251,32 +8253,32 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>06/05/2026 8:11:50 AM</t>
+          <t>06/10/2026 9:43:39 AM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -8300,32 +8302,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>06/04/2026 4:43:41 PM</t>
+          <t>06/10/2026 9:38:39 AM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -8349,38 +8351,38 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>06/04/2026 2:19:48 PM</t>
+          <t>06/10/2026 8:20:12 AM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -8398,32 +8400,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>06/04/2026 9:36:08 AM</t>
+          <t>06/10/2026 7:38:13 AM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -8437,42 +8439,40 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N164" t="n">
+        <v>0.645</v>
       </c>
       <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>06/03/2026 10:39:43 AM</t>
+          <t>06/09/2026 5:08:17 PM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -8496,32 +8496,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>06/02/2026 8:27:02 PM</t>
+          <t>06/08/2026 4:34:35 PM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -8545,17 +8545,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>06/02/2026 6:59:41 PM</t>
+          <t>06/08/2026 11:36:52 AM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -8594,38 +8594,38 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>06/02/2026 2:57:58 PM</t>
+          <t>06/08/2026 8:30:19 AM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -8643,32 +8643,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>06/02/2026 1:08:52 PM</t>
+          <t>06/05/2026 11:50:44 AM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>James Townsel</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
@@ -8682,37 +8682,35 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N169" t="n">
+        <v>0.5649999999999999</v>
       </c>
       <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>06/02/2026 12:48:40 PM</t>
+          <t>06/05/2026 10:45:18 AM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8723,7 +8721,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -8741,32 +8739,32 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>06/02/2026 11:11:57 AM</t>
+          <t>06/05/2026 9:11:54 AM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -8790,28 +8788,32 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>06/01/2026 4:28:39 PM</t>
+          <t>06/05/2026 8:11:50 AM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -8835,32 +8837,32 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>06/01/2026 12:44:20 PM</t>
+          <t>06/04/2026 4:43:41 PM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -8874,31 +8876,37 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="n">
-        <v>0.516</v>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>05/29/2026 5:36:46 PM</t>
+          <t>06/04/2026 2:19:48 PM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Shamonte Jacobs</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8909,7 +8917,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -8927,28 +8935,32 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>05/29/2026 5:35:16 PM</t>
+          <t>06/04/2026 9:36:08 AM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Roderick Bush</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
@@ -8972,28 +8984,32 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>05/29/2026 12:30:16 PM</t>
+          <t>06/03/2026 10:39:43 AM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Robert Ulrich</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>GEG</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -9017,28 +9033,32 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>05/29/2026 10:22:39 AM</t>
+          <t>06/02/2026 8:27:02 PM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -9062,32 +9082,32 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>05/28/2026 11:10:28 AM</t>
+          <t>06/02/2026 6:59:41 PM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -9111,32 +9131,32 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>05/28/2026 7:18:26 AM</t>
+          <t>06/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -9160,32 +9180,32 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>05/27/2026 1:48:23 PM</t>
+          <t>06/02/2026 1:08:52 PM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -9199,46 +9219,48 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="n">
-        <v>0.696</v>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>05/27/2026 1:06:15 PM</t>
+          <t>06/02/2026 12:48:40 PM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -9246,40 +9268,42 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="n">
-        <v>0.513</v>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>05/26/2026 1:23:21 PM</t>
+          <t>06/02/2026 11:11:57 AM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 75</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -9303,32 +9327,28 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>05/22/2026 2:52:48 PM</t>
+          <t>06/01/2026 4:28:39 PM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>RDU</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -9352,32 +9372,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>05/22/2026 10:07:05 AM</t>
+          <t>06/01/2026 12:44:20 PM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
@@ -9391,42 +9411,36 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N184" t="n">
+        <v>0.516</v>
       </c>
       <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>05/22/2026 6:58:39 AM</t>
+          <t>05/29/2026 5:36:46 PM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>RDU</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -9450,32 +9464,28 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>05/21/2026 5:40:30 PM</t>
+          <t>05/29/2026 5:35:16 PM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>PDX</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
@@ -9489,40 +9499,38 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="n">
-        <v>0.636</v>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>05/20/2026 4:28:02 PM</t>
+          <t>05/29/2026 12:30:16 PM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9546,32 +9554,28 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>05/19/2026 2:01:04 PM</t>
+          <t>05/29/2026 10:22:39 AM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -9595,32 +9599,32 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>05/19/2026 12:45:47 PM</t>
+          <t>05/28/2026 11:10:28 AM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Harold Dulaney</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
@@ -9634,10 +9638,204 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="n">
-        <v>0.592</v>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>05/28/2026 7:18:26 AM</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Truck 711</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Shamonte Jacobs</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:48:23 PM</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="O191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>05/27/2026 1:06:15 PM</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Misteer Greene</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>05/26/2026 1:23:21 PM</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Truck 103</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>John Edmonson</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,38 +496,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/20/2026 2:10:00 PM</t>
+          <t>08/21/2026 12:22:04 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,38 +545,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/20/2026 12:19:12 PM</t>
+          <t>08/20/2026 2:10:00 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,27 +594,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/19/2026 12:36:10 PM</t>
+          <t>08/20/2026 12:19:12 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -643,27 +643,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19/2026 11:30:26 AM</t>
+          <t>08/19/2026 12:36:10 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -692,38 +692,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/18/2026 9:06:54 PM</t>
+          <t>08/19/2026 11:30:26 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,32 +741,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/18/2026 9:27:08 AM</t>
+          <t>08/18/2026 9:06:54 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -790,17 +790,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/18/2026 8:29:18 AM</t>
+          <t>08/18/2026 9:27:08 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -815,13 +815,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,38 +839,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/17/2026 2:27:02 PM</t>
+          <t>08/18/2026 8:29:18 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -888,32 +888,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11:17 PM</t>
+          <t>08/17/2026 2:27:02 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -937,32 +937,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/17/2026 10:13:40 AM</t>
+          <t>08/17/2026 12:11:17 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -976,40 +976,42 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.509</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/17/2026 8:30:21 AM</t>
+          <t>08/17/2026 10:13:40 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1023,42 +1025,40 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.509</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/14/2026 4:05:57 PM</t>
+          <t>08/17/2026 8:30:21 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1082,32 +1082,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/14/2026 9:54:11 AM</t>
+          <t>08/14/2026 4:05:57 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/14/2026 9:44:41 AM</t>
+          <t>08/14/2026 9:54:11 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1180,32 +1180,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/13/2026 3:40:10 PM</t>
+          <t>08/14/2026 9:44:41 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1219,40 +1219,42 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0.526</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/13/2026 2:02:16 PM</t>
+          <t>08/13/2026 3:40:10 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1266,37 +1268,35 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>0.526</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/13/2026 9:15:16 AM</t>
+          <t>08/13/2026 2:02:16 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1307,7 +1307,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1325,32 +1325,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/12/2026 4:38:02 PM</t>
+          <t>08/13/2026 9:15:16 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1364,35 +1364,37 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.508</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11/2026 3:50:43 PM</t>
+          <t>08/12/2026 4:38:02 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1403,7 +1405,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1412,39 +1414,39 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>0.658</v>
+        <v>0.508</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/11/2026 3:18:05 PM</t>
+          <t>08/11/2026 3:50:43 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1458,42 +1460,40 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>0.658</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/11/2026 12:59:26 PM</t>
+          <t>08/11/2026 3:18:05 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1517,32 +1517,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/11/2026 9:49:26 AM</t>
+          <t>08/11/2026 12:59:26 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1566,17 +1566,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/10/2026 4:31:38 PM</t>
+          <t>08/11/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1615,17 +1615,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/10/2026 3:59:01 PM</t>
+          <t>08/10/2026 4:31:38 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1664,32 +1664,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/10/2026 10:15:01 AM</t>
+          <t>08/10/2026 3:59:01 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1713,32 +1713,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/10/2026 9:11:35 AM</t>
+          <t>08/10/2026 10:15:01 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/07/2026 8:53:33 AM</t>
+          <t>08/10/2026 9:11:35 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1811,32 +1811,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/06/2026 9:31:18 PM</t>
+          <t>08/07/2026 8:53:33 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1860,38 +1860,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/06/2026 4:43:28 PM</t>
+          <t>08/06/2026 9:31:18 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brian Kelly</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1899,46 +1899,48 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>0.545</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/06/2026 7:30:46 AM</t>
+          <t>08/06/2026 4:43:28 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Brian Kelly</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1946,17 +1948,15 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N31" t="n">
+        <v>0.545</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/06/2026 7:19:47 AM</t>
+          <t>08/06/2026 7:30:46 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2005,38 +2005,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/05/2026 6:26:33 PM</t>
+          <t>08/06/2026 7:19:47 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2044,46 +2044,48 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>0.543</v>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/05/2026 3:11:07 PM</t>
+          <t>08/05/2026 6:26:33 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2091,37 +2093,35 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N34" t="n">
+        <v>0.543</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/05/2026 2:24:40 PM</t>
+          <t>08/05/2026 3:11:07 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2150,32 +2150,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/04/2026 3:18:35 PM</t>
+          <t>08/05/2026 2:24:40 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2199,38 +2199,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/04/2026 9:00:55 AM</t>
+          <t>08/04/2026 3:18:35 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Khali Arrington</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2238,40 +2238,42 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>0.635</v>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/03/2026 7:20:40 PM</t>
+          <t>08/04/2026 9:00:55 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Khali Arrington</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2285,42 +2287,40 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N38" t="n">
+        <v>0.635</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/03/2026 6:58:03 PM</t>
+          <t>08/03/2026 7:20:40 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2334,46 +2334,48 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>0.491</v>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/03/2026 5:25:29 PM</t>
+          <t>08/03/2026 6:58:03 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2381,42 +2383,40 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N40" t="n">
+        <v>0.491</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/03/2026 3:02:06 PM</t>
+          <t>08/03/2026 5:25:29 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2440,38 +2440,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/03/2026 10:53:14 AM</t>
+          <t>08/03/2026 3:02:06 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/03/2026 10:05:29 AM</t>
+          <t>08/03/2026 10:53:14 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/03/2026 9:13:14 AM</t>
+          <t>08/03/2026 10:05:29 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2587,38 +2587,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/03/2026 8:39:15 AM</t>
+          <t>08/03/2026 9:13:14 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2636,32 +2636,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/31/2026 7:09:03 PM</t>
+          <t>08/03/2026 8:39:15 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kurt Purdie</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2675,40 +2675,42 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>0.631</v>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/31/2026 3:39:46 PM</t>
+          <t>07/31/2026 7:09:03 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Kurt Purdie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2722,17 +2724,15 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N47" t="n">
+        <v>0.631</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/31/2026 3:07:50 PM</t>
+          <t>07/31/2026 3:39:46 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2781,32 +2781,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/31/2026 11:18:13 AM</t>
+          <t>07/31/2026 3:07:50 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/31/2026 7:03:13 AM</t>
+          <t>07/31/2026 11:18:13 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2879,32 +2879,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/29/2026 2:23:36 PM</t>
+          <t>07/31/2026 7:03:13 AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/29/2026 1:29:51 PM</t>
+          <t>07/29/2026 2:23:36 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/29/2026 12:50:14 PM</t>
+          <t>07/29/2026 1:29:51 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3026,32 +3026,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/29/2026 10:04:25 AM</t>
+          <t>07/29/2026 12:50:14 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3075,32 +3075,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/28/2026 4:27:30 PM</t>
+          <t>07/29/2026 10:04:25 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3124,38 +3124,38 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/28/2026 3:53:58 PM</t>
+          <t>07/28/2026 4:27:30 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3173,27 +3173,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/28/2026 3:44:54 PM</t>
+          <t>07/28/2026 3:53:58 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3204,7 +3204,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3222,32 +3222,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/28/2026 1:51:55 PM</t>
+          <t>07/28/2026 3:44:54 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3271,27 +3271,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/28/2026 11:42:07 AM</t>
+          <t>07/28/2026 1:51:55 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jerand Townsel</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3320,27 +3320,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/28/2026 11:39:57 AM</t>
+          <t>07/28/2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Jerand Townsel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3369,32 +3369,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/28/2026 10:23:00 AM</t>
+          <t>07/28/2026 11:39:57 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3418,32 +3418,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/28/2026 9:57:45 AM</t>
+          <t>07/28/2026 10:23:00 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3467,27 +3467,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/28/2026 9:11:05 AM</t>
+          <t>07/28/2026 9:57:45 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3516,32 +3516,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/27/2026 5:42:13 PM</t>
+          <t>07/28/2026 9:11:05 AM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Defensive Driving, Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3555,46 +3555,48 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
-        <v>0.529</v>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/27/2026 2:04:05 PM</t>
+          <t>07/27/2026 5:42:13 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Defensive Driving, Harsh Brake</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3602,17 +3604,15 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N65" t="n">
+        <v>0.529</v>
       </c>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/27/2026 12:00:04 PM</t>
+          <t>07/27/2026 2:04:05 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3661,17 +3661,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/27/2026 8:57:57 AM</t>
+          <t>07/27/2026 12:00:04 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3710,17 +3710,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/24/2026 2:10:44 PM</t>
+          <t>07/27/2026 8:57:57 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3759,27 +3759,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/24/2026 10:45:02 AM</t>
+          <t>07/24/2026 2:10:44 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3790,7 +3790,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3808,32 +3808,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/24/2026 10:16:36 AM</t>
+          <t>07/24/2026 10:45:02 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3857,32 +3857,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:49 PM</t>
+          <t>07/24/2026 10:16:36 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/22/2026 5:44:09 PM</t>
+          <t>07/22/2026 8:57:49 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3955,32 +3955,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/21/2026 12:22:30 PM</t>
+          <t>07/22/2026 5:44:09 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRUCK 85</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>John Boerger</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -4004,38 +4004,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/21/2026 12:05:00 PM</t>
+          <t>07/21/2026 12:22:30 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 85</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>John Boerger</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4053,27 +4053,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/21/2026 11:52:20 AM</t>
+          <t>07/21/2026 12:05:00 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4084,7 +4084,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4102,7 +4102,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/20/2026 3:59:36 PM</t>
+          <t>07/21/2026 11:52:20 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4151,38 +4151,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/16/2026 1:36:56 PM</t>
+          <t>07/20/2026 3:59:36 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4200,38 +4200,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/16/2026 1:17:23 PM</t>
+          <t>07/16/2026 1:36:56 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4249,32 +4249,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/15/2026 4:52:33 PM</t>
+          <t>07/16/2026 1:17:23 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4298,27 +4298,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:43 PM</t>
+          <t>07/15/2026 4:52:33 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4347,32 +4347,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:25 PM</t>
+          <t>07/15/2026 3:06:43 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4396,38 +4396,38 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/15/2026 12:15:41 PM</t>
+          <t>07/15/2026 3:06:25 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4445,27 +4445,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/15/2026 12:10:03 PM</t>
+          <t>07/15/2026 12:15:41 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4476,7 +4476,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4494,38 +4494,38 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/15/2026 6:28:32 AM</t>
+          <t>07/15/2026 12:10:03 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4543,38 +4543,38 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/14/2026 7:12:18 PM</t>
+          <t>07/15/2026 6:28:32 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4592,32 +4592,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/14/2026 6:10:58 PM</t>
+          <t>07/14/2026 7:12:18 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -4641,27 +4641,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/14/2026 5:39:20 PM</t>
+          <t>07/14/2026 6:10:58 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/14/2026 5:31:40 PM</t>
+          <t>07/14/2026 5:39:20 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4739,27 +4739,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/14/2026 11:46:20 AM</t>
+          <t>07/14/2026 5:31:40 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4770,7 +4770,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4788,38 +4788,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/14/2026 9:57:18 AM</t>
+          <t>07/14/2026 11:46:20 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4837,32 +4837,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/14/2026 9:13:03 AM</t>
+          <t>07/14/2026 9:57:18 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>truck 703</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4886,27 +4886,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/13/2026 2:41:35 PM</t>
+          <t>07/14/2026 9:13:03 AM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>truck 703</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4935,32 +4935,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/13/2026 1:03:42 PM</t>
+          <t>07/13/2026 2:41:35 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Juan Santiago</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -4984,32 +4984,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/13/2026 12:58:10 PM</t>
+          <t>07/13/2026 1:03:42 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Juan Santiago</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -5033,17 +5033,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/13/2026 12:48:08 PM</t>
+          <t>07/13/2026 12:58:10 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5082,38 +5082,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/13/2026 11:24:44 AM</t>
+          <t>07/13/2026 12:48:08 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5131,38 +5131,38 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/13/2026 10:27:59 AM</t>
+          <t>07/13/2026 11:24:44 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5180,32 +5180,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/12/2026 9:23:11 AM</t>
+          <t>07/13/2026 10:27:59 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OR 70</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5229,38 +5229,38 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/11/2026 8:35:15 AM</t>
+          <t>07/12/2026 9:23:11 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5278,27 +5278,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/10/2026 1:09:28 PM</t>
+          <t>07/11/2026 8:35:15 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5309,7 +5309,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5327,17 +5327,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/10/2026 5:25:49 AM</t>
+          <t>07/10/2026 1:09:28 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/10/2026 4:50:20 AM</t>
+          <t>07/10/2026 5:25:49 AM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -5425,38 +5425,38 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>07/09/2026 7:53:06 PM</t>
+          <t>07/10/2026 4:50:20 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5464,15 +5464,17 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="n">
-        <v>0.671</v>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>07/09/2026 6:59:54 PM</t>
+          <t>07/09/2026 7:53:06 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5497,13 +5499,13 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5511,37 +5513,35 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N104" t="n">
+        <v>0.671</v>
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>07/09/2026 6:21:15 PM</t>
+          <t>07/09/2026 6:59:54 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5552,7 +5552,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5570,32 +5570,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>07/09/2026 12:47:45 PM</t>
+          <t>07/09/2026 6:21:15 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -5619,38 +5619,38 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>07/09/2026 11:55:07 AM</t>
+          <t>07/09/2026 12:47:45 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5668,38 +5668,38 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>07/08/2026 6:29:26 PM</t>
+          <t>07/09/2026 11:55:07 AM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5717,38 +5717,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07/08/2026 11:40:54 AM</t>
+          <t>07/08/2026 6:29:26 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Truck 803</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5766,27 +5766,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>07/08/2026 10:12:05 AM</t>
+          <t>07/08/2026 11:40:54 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 803</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5815,27 +5815,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07/07/2026 8:03:23 PM</t>
+          <t>07/08/2026 10:12:05 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5846,7 +5846,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5864,27 +5864,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07/07/2026 6:38:32 PM</t>
+          <t>07/07/2026 8:03:23 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5913,32 +5913,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07/07/2026 2:48:19 PM</t>
+          <t>07/07/2026 6:38:32 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -5962,32 +5962,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07/06/2026 10:26:03 PM</t>
+          <t>07/07/2026 2:48:19 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -6011,27 +6011,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07/06/2026 7:14:26 AM</t>
+          <t>07/06/2026 10:26:03 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6042,7 +6042,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6060,38 +6060,38 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07/02/2026 5:15:10 PM</t>
+          <t>07/06/2026 7:14:26 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6109,32 +6109,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07/02/2026 1:50:55 PM</t>
+          <t>07/02/2026 5:15:10 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -6158,27 +6158,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07/02/2026 12:25:36 PM</t>
+          <t>07/02/2026 1:50:55 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6189,7 +6189,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6207,38 +6207,38 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07/02/2026 12:22:00 PM</t>
+          <t>07/02/2026 12:25:36 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6256,32 +6256,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07/02/2026 12:00:30 PM</t>
+          <t>07/02/2026 12:22:00 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -6295,46 +6295,48 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="n">
-        <v>0.534</v>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07/02/2026 11:56:44 AM</t>
+          <t>07/02/2026 12:00:30 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6342,37 +6344,35 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N121" t="n">
+        <v>0.534</v>
       </c>
       <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07/02/2026 11:03:25 AM</t>
+          <t>07/02/2026 11:56:44 AM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TRUCK 67</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6383,7 +6383,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6401,27 +6401,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07/01/2026 6:08:17 PM</t>
+          <t>07/02/2026 11:03:25 AM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>TRUCK 67</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6432,7 +6432,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6450,27 +6450,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07/01/2026 3:07:51 PM</t>
+          <t>07/01/2026 6:08:17 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6499,27 +6499,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07/01/2026 1:29:57 PM</t>
+          <t>07/01/2026 3:07:51 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6548,17 +6548,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07/01/2026 12:10:49 PM</t>
+          <t>07/01/2026 1:29:57 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07/01/2026 9:29:37 AM</t>
+          <t>07/01/2026 12:10:49 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -6636,46 +6636,48 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="n">
-        <v>0.708</v>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/30/2026 12:19:45 PM</t>
+          <t>07/01/2026 9:29:37 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6683,48 +6685,46 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N128" t="n">
+        <v>0.708</v>
       </c>
       <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/30/2026 8:20:51 AM</t>
+          <t>06/30/2026 12:19:45 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>John Moore</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -6742,17 +6742,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/29/2026 1:07:28 PM</t>
+          <t>06/30/2026 8:20:51 AM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/29/2026 4:14:57 AM</t>
+          <t>06/29/2026 1:07:28 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6840,32 +6840,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/26/2026 1:15:05 PM</t>
+          <t>06/29/2026 4:14:57 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -6879,40 +6879,42 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="n">
-        <v>0.597</v>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>06/26/2026 12:30:38 PM</t>
+          <t>06/26/2026 1:15:05 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -6926,37 +6928,35 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" t="n">
+        <v>0.597</v>
       </c>
       <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>06/26/2026 11:53:52 AM</t>
+          <t>06/26/2026 12:30:38 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6985,38 +6985,38 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>06/26/2026 9:29:14 AM</t>
+          <t>06/26/2026 11:53:52 AM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7034,38 +7034,38 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06/25/2026 7:20:50 PM</t>
+          <t>06/26/2026 9:29:14 AM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>06/24/2026 6:03:00 PM</t>
+          <t>06/25/2026 7:20:50 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7132,27 +7132,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>06/24/2026 11:16:24 AM</t>
+          <t>06/24/2026 6:03:00 PM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7181,27 +7181,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>06/24/2026 10:02:37 AM</t>
+          <t>06/24/2026 11:16:24 AM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7212,7 +7212,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7230,27 +7230,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>06/23/2026 11:23:16 AM</t>
+          <t>06/24/2026 10:02:37 AM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7279,27 +7279,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>06/20/2026 7:57:27 PM</t>
+          <t>06/23/2026 11:23:16 AM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7310,7 +7310,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -7328,32 +7328,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>06/19/2026 2:31:31 PM</t>
+          <t>06/20/2026 7:57:27 PM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -7367,40 +7367,42 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="n">
-        <v>0.593</v>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>06/19/2026 8:15:23 AM</t>
+          <t>06/19/2026 2:31:31 PM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -7414,42 +7416,40 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N143" t="n">
+        <v>0.593</v>
       </c>
       <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>06/18/2026 9:09:41 AM</t>
+          <t>06/19/2026 8:15:23 AM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 202</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Wade DeHaven</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -7473,7 +7473,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>06/18/2026 9:00:54 AM</t>
+          <t>06/18/2026 9:09:41 AM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7522,7 +7522,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>06/18/2026 7:29:06 AM</t>
+          <t>06/18/2026 9:00:54 AM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7571,7 +7571,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>06/17/2026 12:51:55 PM</t>
+          <t>06/18/2026 7:29:06 AM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -7620,32 +7620,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>06/17/2026 12:24:03 PM</t>
+          <t>06/17/2026 12:51:55 PM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -7669,7 +7669,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/17/2026 12:24:03 PM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -7718,38 +7718,38 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06/16/2026 4:15:38 PM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -7757,40 +7757,42 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="n">
-        <v>0.829</v>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>06/16/2026 1:51:18 PM</t>
+          <t>06/16/2026 4:15:38 PM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -7804,48 +7806,46 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N151" t="n">
+        <v>0.829</v>
       </c>
       <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>06/15/2026 4:48:21 PM</t>
+          <t>06/16/2026 1:51:18 PM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -7863,12 +7863,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>06/12/2026 1:49:28 PM</t>
+          <t>06/15/2026 4:48:21 PM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7888,13 +7888,13 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -7912,32 +7912,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>06/12/2026 1:29:37 PM</t>
+          <t>06/12/2026 1:49:28 PM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -7961,38 +7961,38 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>06/12/2026 12:42:44 PM</t>
+          <t>06/12/2026 1:29:37 PM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -8010,38 +8010,38 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51:49 AM</t>
+          <t>06/12/2026 12:42:44 PM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -8049,46 +8049,48 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="n">
-        <v>0.775</v>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>06/12/2026 9:18:27 AM</t>
+          <t>06/12/2026 10:51:49 AM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -8096,17 +8098,15 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N157" t="n">
+        <v>0.775</v>
       </c>
       <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>06/11/2026 1:13:47 PM</t>
+          <t>06/12/2026 9:18:27 AM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8155,38 +8155,38 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>06/10/2026 2:13:04 PM</t>
+          <t>06/11/2026 1:13:47 PM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -8204,38 +8204,38 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>06/10/2026 12:24:28 PM</t>
+          <t>06/10/2026 2:13:04 PM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -8253,32 +8253,32 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>06/10/2026 9:43:39 AM</t>
+          <t>06/10/2026 12:24:28 PM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -8302,7 +8302,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>06/10/2026 9:38:39 AM</t>
+          <t>06/10/2026 9:43:39 AM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8351,32 +8351,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>06/10/2026 8:20:12 AM</t>
+          <t>06/10/2026 9:38:39 AM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -8400,32 +8400,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>06/10/2026 7:38:13 AM</t>
+          <t>06/10/2026 8:20:12 AM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -8439,40 +8439,42 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="n">
-        <v>0.645</v>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>06/09/2026 5:08:17 PM</t>
+          <t>06/10/2026 7:38:13 AM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -8486,17 +8488,15 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N165" t="n">
+        <v>0.645</v>
       </c>
       <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>06/08/2026 4:34:35 PM</t>
+          <t>06/09/2026 5:08:17 PM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -8545,27 +8545,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>06/08/2026 11:36:52 AM</t>
+          <t>06/08/2026 4:34:35 PM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8594,17 +8594,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>06/08/2026 8:30:19 AM</t>
+          <t>06/08/2026 11:36:52 AM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8619,13 +8619,13 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -8643,38 +8643,38 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>06/05/2026 11:50:44 AM</t>
+          <t>06/08/2026 8:30:19 AM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>James Townsel</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -8682,40 +8682,42 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="n">
-        <v>0.5649999999999999</v>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>06/05/2026 10:45:18 AM</t>
+          <t>06/05/2026 11:50:44 AM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>James Townsel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
@@ -8729,42 +8731,40 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N170" t="n">
+        <v>0.5649999999999999</v>
       </c>
       <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>06/05/2026 9:11:54 AM</t>
+          <t>06/05/2026 10:45:18 AM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -8788,7 +8788,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>06/05/2026 8:11:50 AM</t>
+          <t>06/05/2026 9:11:54 AM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>06/04/2026 4:43:41 PM</t>
+          <t>06/05/2026 8:11:50 AM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -8886,38 +8886,38 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>06/04/2026 2:19:48 PM</t>
+          <t>06/04/2026 4:43:41 PM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -8935,38 +8935,38 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>06/04/2026 9:36:08 AM</t>
+          <t>06/04/2026 2:19:48 PM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -8984,32 +8984,32 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>06/03/2026 10:39:43 AM</t>
+          <t>06/04/2026 9:36:08 AM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -9033,32 +9033,32 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>06/02/2026 8:27:02 PM</t>
+          <t>06/03/2026 10:39:43 AM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -9082,7 +9082,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>06/02/2026 6:59:41 PM</t>
+          <t>06/02/2026 8:27:02 PM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9131,32 +9131,32 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>06/02/2026 2:57:58 PM</t>
+          <t>06/02/2026 6:59:41 PM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>06/02/2026 1:08:52 PM</t>
+          <t>06/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9229,38 +9229,38 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>06/02/2026 12:48:40 PM</t>
+          <t>06/02/2026 1:08:52 PM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -9278,27 +9278,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>06/02/2026 11:11:57 AM</t>
+          <t>06/02/2026 12:48:40 PM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9309,7 +9309,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -9327,23 +9327,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>06/01/2026 4:28:39 PM</t>
+          <t>06/02/2026 11:11:57 AM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 75</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -9372,32 +9376,28 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>06/01/2026 12:44:20 PM</t>
+          <t>06/01/2026 4:28:39 PM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
         <is>
           <t>GEG</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>GEG, PDX</t>
-        </is>
-      </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
@@ -9411,15 +9411,17 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="n">
-        <v>0.516</v>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>05/29/2026 5:36:46 PM</t>
+          <t>06/01/2026 12:44:20 PM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9429,10 +9431,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Robert Ulrich</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>GEG</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>GEG, PDX</t>
@@ -9440,7 +9446,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -9454,17 +9460,15 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N185" t="n">
+        <v>0.516</v>
       </c>
       <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>05/29/2026 5:35:16 PM</t>
+          <t>05/29/2026 5:36:46 PM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9509,7 +9513,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>05/29/2026 12:30:16 PM</t>
+          <t>05/29/2026 5:35:16 PM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9554,7 +9558,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>05/29/2026 10:22:39 AM</t>
+          <t>05/29/2026 12:30:16 PM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9599,32 +9603,28 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>05/28/2026 11:10:28 AM</t>
+          <t>05/29/2026 10:22:39 AM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>Stephen King</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
@@ -9648,32 +9648,32 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>05/28/2026 7:18:26 AM</t>
+          <t>05/28/2026 11:10:28 AM</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
@@ -9697,32 +9697,32 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>05/27/2026 1:48:23 PM</t>
+          <t>05/28/2026 7:18:26 AM</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -9736,15 +9736,17 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="n">
-        <v>0.696</v>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>05/27/2026 1:06:15 PM</t>
+          <t>05/27/2026 1:48:23 PM</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9784,39 +9786,39 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
-        <v>0.513</v>
+        <v>0.696</v>
       </c>
       <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>05/26/2026 1:23:21 PM</t>
+          <t>05/27/2026 1:06:15 PM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 75</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
@@ -9830,12 +9832,59 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N193" t="n">
+        <v>0.513</v>
       </c>
       <c r="O193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>05/26/2026 1:23:21 PM</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Truck 103</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>John Edmonson</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O194"/>
+  <dimension ref="A1:O198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:22:04 PM</t>
+          <t>08/29/2026 9:01:37 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -545,12 +545,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/20/2026 2:10:00 PM</t>
+          <t>08/28/2026 3:53:05 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,13 +570,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,32 +594,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/20/2026 12:19:12 PM</t>
+          <t>08/28/2026 1:55:25 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -643,27 +643,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19/2026 12:36:10 PM</t>
+          <t>08/28/2026 1:54:02 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -692,38 +692,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/19/2026 11:30:26 AM</t>
+          <t>08/27/2026 3:11:21 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,32 +741,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/18/2026 9:06:54 PM</t>
+          <t>08/27/2026 11:46:53 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -790,32 +790,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/18/2026 9:27:08 AM</t>
+          <t>08/27/2026 11:38:47 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -829,17 +829,15 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>0.5580000000000001</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/18/2026 8:29:18 AM</t>
+          <t>08/27/2026 8:16:34 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -849,7 +847,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,13 +862,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -888,7 +886,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/17/2026 2:27:02 PM</t>
+          <t>08/26/2026 5:08:10 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -937,38 +935,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11:17 PM</t>
+          <t>08/26/2026 4:27:03 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 83</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jose Hondolero</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>Truck 96</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -986,32 +976,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/17/2026 10:13:40 AM</t>
+          <t>08/26/2026 4:22:00 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1025,46 +1015,48 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.509</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/17/2026 8:30:21 AM</t>
+          <t>08/26/2026 12:12:10 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>TRUCK 56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1082,38 +1074,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/14/2026 4:05:57 PM</t>
+          <t>08/25/2026 8:29:38 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN, SLC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1131,27 +1123,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/14/2026 9:54:11 AM</t>
+          <t>08/24/2026 4:30:33 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1162,7 +1154,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1180,27 +1172,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/14/2026 9:44:41 AM</t>
+          <t>08/21/2026 12:22:04 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1229,32 +1221,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/13/2026 3:40:10 PM</t>
+          <t>08/20/2026 2:10:00 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1268,35 +1260,37 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.526</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/13/2026 2:02:16 PM</t>
+          <t>08/20/2026 12:19:12 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1307,7 +1301,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1325,27 +1319,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/13/2026 9:15:16 AM</t>
+          <t>08/19/2026 12:36:10 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1356,7 +1350,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1374,7 +1368,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/12/2026 4:38:02 PM</t>
+          <t>08/19/2026 11:30:26 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1384,7 +1378,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1399,13 +1393,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1413,40 +1407,42 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>0.508</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/11/2026 3:50:43 PM</t>
+          <t>08/19/2026 11:04:13 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 707</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Jacob Castleberry</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ABI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ABI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1461,39 +1457,39 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>0.658</v>
+        <v>0.547</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/11/2026 3:18:05 PM</t>
+          <t>08/18/2026 9:06:54 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1517,7 +1513,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/11/2026 12:59:26 PM</t>
+          <t>08/18/2026 9:27:08 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1542,7 +1538,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1566,38 +1562,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/11/2026 9:49:26 AM</t>
+          <t>08/18/2026 8:29:18 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1615,27 +1611,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/10/2026 4:31:38 PM</t>
+          <t>08/17/2026 2:27:02 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oscar Hong</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1664,7 +1660,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/10/2026 3:59:01 PM</t>
+          <t>08/17/2026 12:11:17 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1713,32 +1709,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/10/2026 10:15:01 AM</t>
+          <t>08/17/2026 10:13:40 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1752,27 +1748,25 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" t="n">
+        <v>0.509</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/10/2026 9:11:35 AM</t>
+          <t>08/17/2026 8:30:21 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1787,7 +1781,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1811,32 +1805,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/07/2026 8:53:33 AM</t>
+          <t>08/14/2026 4:05:57 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1860,32 +1854,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/06/2026 9:31:18 PM</t>
+          <t>08/14/2026 9:54:11 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 83</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1909,38 +1903,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/06/2026 4:43:28 PM</t>
+          <t>08/14/2026 9:44:41 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brian Kelly</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1948,40 +1942,42 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>0.545</v>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/06/2026 7:30:46 AM</t>
+          <t>08/13/2026 3:40:10 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1995,37 +1991,35 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N32" t="n">
+        <v>0.526</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/06/2026 7:19:47 AM</t>
+          <t>08/13/2026 2:02:16 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2054,32 +2048,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/05/2026 6:26:33 PM</t>
+          <t>08/13/2026 9:15:16 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2093,46 +2087,48 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>0.543</v>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/05/2026 3:11:07 PM</t>
+          <t>08/12/2026 4:38:02 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2140,42 +2136,40 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N35" t="n">
+        <v>0.508</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/05/2026 2:24:40 PM</t>
+          <t>08/11/2026 3:50:43 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2189,37 +2183,35 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.658</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/04/2026 3:18:35 PM</t>
+          <t>08/11/2026 3:18:05 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2248,38 +2240,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/04/2026 9:00:55 AM</t>
+          <t>08/11/2026 12:59:26 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 77</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Khali Arrington</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2287,46 +2279,48 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>0.635</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/03/2026 7:20:40 PM</t>
+          <t>08/11/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2344,38 +2338,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/03/2026 6:58:03 PM</t>
+          <t>08/10/2026 4:31:38 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Oscar Hong</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2383,25 +2377,27 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>0.491</v>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/03/2026 5:25:29 PM</t>
+          <t>08/10/2026 3:59:01 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2416,7 +2412,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2440,32 +2436,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/03/2026 3:02:06 PM</t>
+          <t>08/10/2026 10:15:01 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2489,27 +2485,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/03/2026 10:53:14 AM</t>
+          <t>08/10/2026 9:11:35 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2520,7 +2516,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2538,38 +2534,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/03/2026 10:05:29 AM</t>
+          <t>08/07/2026 8:53:33 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2587,38 +2583,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/03/2026 9:13:14 AM</t>
+          <t>08/06/2026 9:31:18 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 83</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Jose Hondolero</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2636,38 +2632,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/03/2026 8:39:15 AM</t>
+          <t>08/06/2026 4:43:28 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Brian Kelly</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2675,42 +2671,40 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N46" t="n">
+        <v>0.545</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/31/2026 7:09:03 PM</t>
+          <t>08/06/2026 7:30:46 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kurt Purdie</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2724,40 +2718,42 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
-        <v>0.631</v>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/31/2026 3:39:46 PM</t>
+          <t>08/06/2026 7:19:47 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2781,38 +2777,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/31/2026 3:07:50 PM</t>
+          <t>08/05/2026 6:26:33 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2820,37 +2816,35 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N49" t="n">
+        <v>0.543</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/31/2026 11:18:13 AM</t>
+          <t>08/05/2026 3:11:07 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2879,32 +2873,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/31/2026 7:03:13 AM</t>
+          <t>08/05/2026 2:24:40 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>RDU</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2928,27 +2918,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/29/2026 2:23:36 PM</t>
+          <t>08/04/2026 3:18:35 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2977,17 +2967,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/29/2026 1:29:51 PM</t>
+          <t>08/04/2026 9:00:55 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 77</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Khali Arrington</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3002,13 +2992,13 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3016,48 +3006,46 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N53" t="n">
+        <v>0.635</v>
       </c>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/29/2026 12:50:14 PM</t>
+          <t>08/03/2026 7:20:40 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3075,38 +3063,38 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/29/2026 10:04:25 AM</t>
+          <t>08/03/2026 6:58:03 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3114,37 +3102,35 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N55" t="n">
+        <v>0.491</v>
       </c>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/28/2026 4:27:30 PM</t>
+          <t>08/03/2026 5:25:29 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3173,7 +3159,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/28/2026 3:53:58 PM</t>
+          <t>08/03/2026 3:02:06 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3198,13 +3184,13 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3222,27 +3208,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/28/2026 3:44:54 PM</t>
+          <t>08/03/2026 10:53:14 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3253,7 +3239,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3271,17 +3257,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/28/2026 1:51:55 PM</t>
+          <t>08/03/2026 10:05:29 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3296,13 +3282,13 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3320,38 +3306,38 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/28/2026 11:42:07 AM</t>
+          <t>08/03/2026 9:13:14 AM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jerand Townsel</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3369,32 +3355,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/28/2026 11:39:57 AM</t>
+          <t>08/03/2026 8:39:15 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3418,32 +3404,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/28/2026 10:23:00 AM</t>
+          <t>07/31/2026 7:09:03 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Kurt Purdie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3457,42 +3443,40 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N62" t="n">
+        <v>0.631</v>
       </c>
       <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/28/2026 9:57:45 AM</t>
+          <t>07/31/2026 3:39:46 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3516,32 +3500,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/28/2026 9:11:05 AM</t>
+          <t>07/31/2026 3:07:50 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3565,32 +3549,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/27/2026 5:42:13 PM</t>
+          <t>07/31/2026 11:18:13 AM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Defensive Driving, Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3604,25 +3588,27 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>0.529</v>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/27/2026 2:04:05 PM</t>
+          <t>07/31/2026 7:03:13 AM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3637,13 +3623,13 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3661,38 +3647,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/27/2026 12:00:04 PM</t>
+          <t>07/29/2026 2:23:36 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3710,38 +3696,38 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/27/2026 8:57:57 AM</t>
+          <t>07/29/2026 1:29:51 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3759,38 +3745,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/24/2026 2:10:44 PM</t>
+          <t>07/29/2026 12:50:14 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3808,27 +3794,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/24/2026 10:45:02 AM</t>
+          <t>07/29/2026 10:04:25 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3857,32 +3843,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/24/2026 10:16:36 AM</t>
+          <t>07/28/2026 4:27:30 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3906,38 +3892,38 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:49 PM</t>
+          <t>07/28/2026 3:53:58 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3955,27 +3941,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/22/2026 5:44:09 PM</t>
+          <t>07/28/2026 3:44:54 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4004,32 +3990,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/21/2026 12:22:30 PM</t>
+          <t>07/28/2026 1:51:55 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRUCK 85</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>John Boerger</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4053,38 +4039,38 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/21/2026 12:05:00 PM</t>
+          <t>07/28/2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>709</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Jerand Townsel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4102,32 +4088,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/21/2026 11:52:20 AM</t>
+          <t>07/28/2026 11:39:57 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4151,32 +4137,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/20/2026 3:59:36 PM</t>
+          <t>07/28/2026 10:23:00 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4200,27 +4186,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/16/2026 1:36:56 PM</t>
+          <t>07/28/2026 9:57:45 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4231,7 +4217,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4249,32 +4235,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/16/2026 1:17:23 PM</t>
+          <t>07/28/2026 9:11:05 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4298,32 +4284,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/15/2026 4:52:33 PM</t>
+          <t>07/27/2026 5:42:13 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Defensive Driving, Harsh Brake</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -4337,48 +4323,46 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" t="n">
+        <v>0.529</v>
       </c>
       <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:43 PM</t>
+          <t>07/27/2026 2:04:05 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4396,38 +4380,38 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/15/2026 3:06:25 PM</t>
+          <t>07/27/2026 12:00:04 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4445,7 +4429,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/15/2026 12:15:41 PM</t>
+          <t>07/27/2026 8:57:57 AM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4455,7 +4439,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4494,27 +4478,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/15/2026 12:10:03 PM</t>
+          <t>07/24/2026 2:10:44 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4525,7 +4509,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4543,38 +4527,38 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/15/2026 6:28:32 AM</t>
+          <t>07/24/2026 10:45:02 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4592,32 +4576,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/14/2026 7:12:18 PM</t>
+          <t>07/24/2026 10:16:36 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -4641,32 +4625,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/14/2026 6:10:58 PM</t>
+          <t>07/22/2026 8:57:49 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>GEG</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4690,7 +4670,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/14/2026 5:39:20 PM</t>
+          <t>07/22/2026 5:44:09 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4700,14 +4680,10 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SLC</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>SLC</t>
@@ -4739,32 +4715,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/14/2026 5:31:40 PM</t>
+          <t>07/21/2026 12:22:30 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>TRUCK 85</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>John Boerger</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4788,27 +4764,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/14/2026 11:46:20 AM</t>
+          <t>07/21/2026 12:05:00 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Karon King</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4837,32 +4813,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/14/2026 9:57:18 AM</t>
+          <t>07/21/2026 11:52:20 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>GEG</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4886,32 +4858,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/14/2026 9:13:03 AM</t>
+          <t>07/20/2026 3:59:36 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>truck 703</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deadrian Thomas</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -4935,17 +4903,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/13/2026 2:41:35 PM</t>
+          <t>07/16/2026 1:36:56 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4984,38 +4952,38 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/13/2026 1:03:42 PM</t>
+          <t>07/16/2026 1:17:23 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Juan Santiago</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5033,27 +5001,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/13/2026 12:58:10 PM</t>
+          <t>07/15/2026 4:52:33 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5064,7 +5032,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5082,27 +5050,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/13/2026 12:48:08 PM</t>
+          <t>07/15/2026 3:06:43 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5113,7 +5081,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5131,32 +5099,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/13/2026 11:24:44 AM</t>
+          <t>07/15/2026 3:06:25 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Truck 804</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -5180,7 +5148,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/13/2026 10:27:59 AM</t>
+          <t>07/15/2026 12:15:41 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5190,7 +5158,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5205,7 +5173,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5229,38 +5197,34 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/12/2026 9:23:11 AM</t>
+          <t>07/15/2026 12:10:03 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OR 70</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Andrew Fierro</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>PDX</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5278,38 +5242,38 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/11/2026 8:35:15 AM</t>
+          <t>07/15/2026 6:28:32 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5327,38 +5291,38 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/10/2026 1:09:28 PM</t>
+          <t>07/14/2026 7:12:18 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5376,27 +5340,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/10/2026 5:25:49 AM</t>
+          <t>07/14/2026 6:10:58 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5407,7 +5371,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5425,38 +5389,38 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>07/10/2026 4:50:20 AM</t>
+          <t>07/14/2026 5:39:20 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN, SLC</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5474,32 +5438,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>07/09/2026 7:53:06 PM</t>
+          <t>07/14/2026 5:31:40 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN, SLC</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -5513,35 +5477,37 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="n">
-        <v>0.671</v>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>07/09/2026 6:59:54 PM</t>
+          <t>07/14/2026 11:46:20 AM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Truck 79</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Karon King</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5570,32 +5536,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>07/09/2026 6:21:15 PM</t>
+          <t>07/14/2026 9:57:18 AM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -5619,32 +5585,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>07/09/2026 12:47:45 PM</t>
+          <t>07/14/2026 9:13:03 AM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>truck 703</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Deadrian Thomas</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -5668,7 +5634,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>07/09/2026 11:55:07 AM</t>
+          <t>07/13/2026 2:41:35 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5717,38 +5683,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07/08/2026 6:29:26 PM</t>
+          <t>07/13/2026 1:03:42 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Juan Santiago</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5766,27 +5732,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>07/08/2026 11:40:54 AM</t>
+          <t>07/13/2026 12:58:10 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Truck 803</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Damien Dunbar</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MSY</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5815,17 +5781,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07/08/2026 10:12:05 AM</t>
+          <t>07/13/2026 12:48:08 PM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5864,32 +5830,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07/07/2026 8:03:23 PM</t>
+          <t>07/13/2026 11:24:44 AM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 804</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Samuel Bracho</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -5913,38 +5879,38 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07/07/2026 6:38:32 PM</t>
+          <t>07/13/2026 10:27:59 AM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5962,38 +5928,38 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07/07/2026 2:48:19 PM</t>
+          <t>07/12/2026 9:23:11 AM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>OR 70</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Andrew Fierro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6011,27 +5977,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07/06/2026 10:26:03 PM</t>
+          <t>07/11/2026 8:35:15 AM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 103</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>John Edmonson</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6060,12 +6026,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07/06/2026 7:14:26 AM</t>
+          <t>07/10/2026 1:09:28 PM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6109,38 +6075,38 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07/02/2026 5:15:10 PM</t>
+          <t>07/10/2026 5:25:49 AM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6158,38 +6124,38 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07/02/2026 1:50:55 PM</t>
+          <t>07/10/2026 4:50:20 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6207,38 +6173,38 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07/02/2026 12:25:36 PM</t>
+          <t>07/09/2026 7:53:06 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DESHAWN SKIPWITH</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6246,48 +6212,46 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N119" t="n">
+        <v>0.671</v>
       </c>
       <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07/02/2026 12:22:00 PM</t>
+          <t>07/09/2026 6:59:54 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 79</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6305,17 +6269,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07/02/2026 12:00:30 PM</t>
+          <t>07/09/2026 6:21:15 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Michael Reynoso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6330,7 +6294,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -6344,46 +6308,48 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
-        <v>0.534</v>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07/02/2026 11:56:44 AM</t>
+          <t>07/09/2026 12:47:45 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 80</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Roy Carney</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6401,27 +6367,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07/02/2026 11:03:25 AM</t>
+          <t>07/09/2026 11:55:07 AM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TRUCK 67</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6432,7 +6398,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6450,38 +6416,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07/01/2026 6:08:17 PM</t>
+          <t>07/08/2026 6:29:26 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Truck 102</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>David Doney</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6499,27 +6465,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07/01/2026 3:07:51 PM</t>
+          <t>07/08/2026 11:40:54 AM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Truck 99</t>
+          <t>Truck 803</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>Damien Dunbar</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MSY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6548,17 +6514,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07/01/2026 1:29:57 PM</t>
+          <t>07/08/2026 10:12:05 AM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6597,27 +6563,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07/01/2026 12:10:49 PM</t>
+          <t>07/07/2026 8:03:23 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Samuel Bracho</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN, SLC</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6628,7 +6594,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6646,38 +6612,38 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>07/01/2026 9:29:37 AM</t>
+          <t>07/07/2026 6:38:32 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6685,40 +6651,42 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="n">
-        <v>0.708</v>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/30/2026 12:19:45 PM</t>
+          <t>07/07/2026 2:48:19 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>John Moore</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -6742,38 +6710,38 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/30/2026 8:20:51 AM</t>
+          <t>07/06/2026 10:26:03 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -6791,7 +6759,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/29/2026 1:07:28 PM</t>
+          <t>07/06/2026 7:14:26 AM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6816,7 +6784,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -6840,27 +6808,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/29/2026 4:14:57 AM</t>
+          <t>07/02/2026 5:15:10 PM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6871,7 +6839,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6889,17 +6857,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>06/26/2026 1:15:05 PM</t>
+          <t>07/02/2026 1:50:55 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Truck 90</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Joseph Hartmeier</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6914,13 +6882,13 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -6928,40 +6896,42 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
-        <v>0.597</v>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>06/26/2026 12:30:38 PM</t>
+          <t>07/02/2026 12:25:36 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>DESHAWN SKIPWITH</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -6985,38 +6955,38 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>06/26/2026 11:53:52 AM</t>
+          <t>07/02/2026 12:22:00 PM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7034,32 +7004,28 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06/26/2026 9:29:14 AM</t>
+          <t>07/02/2026 12:00:30 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TRUCK 91</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bjorn Pinney</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
+          <t>John Moore</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -7073,42 +7039,40 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N136" t="n">
+        <v>0.534</v>
       </c>
       <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>06/25/2026 7:20:50 PM</t>
+          <t>07/02/2026 11:56:44 AM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Truck 100</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mykiel James</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -7132,17 +7096,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>06/24/2026 6:03:00 PM</t>
+          <t>07/02/2026 11:03:25 AM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TRUCK 81</t>
+          <t>TRUCK 67</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7157,7 +7121,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -7181,38 +7145,38 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>06/24/2026 11:16:24 AM</t>
+          <t>07/01/2026 6:08:17 PM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Truck 66</t>
+          <t>Truck 102</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>David Doney</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7230,17 +7194,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>06/24/2026 10:02:37 AM</t>
+          <t>07/01/2026 3:07:51 PM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>Truck 99</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7255,7 +7219,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -7279,17 +7243,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>06/23/2026 11:23:16 AM</t>
+          <t>07/01/2026 1:29:57 PM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Charles Smith</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7304,7 +7268,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -7328,38 +7292,38 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>06/20/2026 7:57:27 PM</t>
+          <t>07/01/2026 12:10:49 PM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Robert Hong</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7377,27 +7341,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>06/19/2026 2:31:31 PM</t>
+          <t>07/01/2026 9:29:37 AM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kevin Richardson</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7408,7 +7372,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7417,39 +7381,35 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>0.593</v>
+        <v>0.708</v>
       </c>
       <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>06/19/2026 8:15:23 AM</t>
+          <t>06/30/2026 12:19:45 PM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Truck 202</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wade DeHaven</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>BNA</t>
-        </is>
-      </c>
+          <t>John Moore</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -7473,38 +7433,38 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>06/18/2026 9:09:41 AM</t>
+          <t>06/30/2026 8:20:51 AM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 710</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -7522,38 +7482,38 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>06/18/2026 9:00:54 AM</t>
+          <t>06/29/2026 1:07:28 PM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -7571,38 +7531,38 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>06/18/2026 7:29:06 AM</t>
+          <t>06/29/2026 4:14:57 AM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -7620,38 +7580,38 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>06/17/2026 12:51:55 PM</t>
+          <t>06/26/2026 1:15:05 PM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>truck 706</t>
+          <t>Truck 90</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
+          <t>Joseph Hartmeier</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -7659,48 +7619,46 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N148" t="n">
+        <v>0.597</v>
       </c>
       <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06/17/2026 12:24:03 PM</t>
+          <t>06/26/2026 12:30:38 PM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Misteer Greene</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -7718,38 +7676,38 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/26/2026 11:53:52 AM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>KARVELL OLIVER</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -7767,38 +7725,38 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>06/16/2026 4:15:38 PM</t>
+          <t>06/26/2026 9:29:14 AM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 91</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Matthew Pickett</t>
+          <t>Bjorn Pinney</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -7806,40 +7764,42 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="n">
-        <v>0.829</v>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>06/16/2026 1:51:18 PM</t>
+          <t>06/25/2026 7:20:50 PM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>Truck 100</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Mykiel James</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -7863,32 +7823,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>06/15/2026 4:48:21 PM</t>
+          <t>06/24/2026 6:03:00 PM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>V9</t>
+          <t>TRUCK 81</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -7912,38 +7872,38 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>06/12/2026 1:49:28 PM</t>
+          <t>06/24/2026 11:16:24 AM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 66</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -7961,27 +7921,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>06/12/2026 1:29:37 PM</t>
+          <t>06/24/2026 10:02:37 AM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Truck 704</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8010,38 +7970,38 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>06/12/2026 12:42:44 PM</t>
+          <t>06/23/2026 11:23:16 AM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
+          <t>Charles Smith</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -8059,38 +8019,38 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51:49 AM</t>
+          <t>06/20/2026 7:57:27 PM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Truck 86</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Robert Rhodes</t>
+          <t>Robert Hong</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -8098,40 +8058,42 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="n">
-        <v>0.775</v>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>06/12/2026 9:18:27 AM</t>
+          <t>06/19/2026 2:31:31 PM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Kevin Richardson</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -8145,42 +8107,40 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N158" t="n">
+        <v>0.593</v>
       </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>06/11/2026 1:13:47 PM</t>
+          <t>06/19/2026 8:15:23 AM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 202</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Christian Davidson</t>
+          <t>Wade DeHaven</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -8204,38 +8164,38 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>06/10/2026 2:13:04 PM</t>
+          <t>06/18/2026 9:09:41 AM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -8253,27 +8213,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>06/10/2026 12:24:28 PM</t>
+          <t>06/18/2026 9:00:54 AM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8302,32 +8262,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>06/10/2026 9:43:39 AM</t>
+          <t>06/18/2026 7:29:06 AM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -8351,32 +8311,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>06/10/2026 9:38:39 AM</t>
+          <t>06/17/2026 12:51:55 PM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>truck 706</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -8400,7 +8360,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>06/10/2026 8:20:12 AM</t>
+          <t>06/17/2026 12:24:03 PM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8413,19 +8373,15 @@
           <t>Sebastion Franco</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
         <is>
           <t>SLC</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>SLC</t>
-        </is>
-      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -8449,32 +8405,28 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>06/10/2026 7:38:13 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Truck 104</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Randy Fennell</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -8488,46 +8440,48 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="n">
-        <v>0.645</v>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>06/09/2026 5:08:17 PM</t>
+          <t>06/16/2026 4:15:38 PM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 800</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Matthew Pickett</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG, PDX</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -8535,37 +8489,35 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N166" t="n">
+        <v>0.829</v>
       </c>
       <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>06/08/2026 4:34:35 PM</t>
+          <t>06/16/2026 1:51:18 PM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Truck 78</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8576,7 +8528,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -8594,32 +8546,32 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>06/08/2026 11:36:52 AM</t>
+          <t>06/15/2026 4:48:21 PM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Truck 96</t>
+          <t>V9</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Blake Lewis</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
@@ -8643,32 +8595,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>06/08/2026 8:30:19 AM</t>
+          <t>06/12/2026 1:49:28 PM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Michael Reynoso</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
@@ -8692,38 +8644,38 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>06/05/2026 11:50:44 AM</t>
+          <t>06/12/2026 1:29:37 PM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Truck 802</t>
+          <t>Truck 704</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>James Townsel</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -8731,40 +8683,42 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="n">
-        <v>0.5649999999999999</v>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>06/05/2026 10:45:18 AM</t>
+          <t>06/12/2026 12:42:44 PM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TRUCK 84</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jose Hondolero</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -8788,38 +8742,38 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>06/05/2026 9:11:54 AM</t>
+          <t>06/12/2026 10:51:49 AM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TRUCK 74</t>
+          <t>Truck 86</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Robert Rhodes</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -8827,17 +8781,15 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N172" t="n">
+        <v>0.775</v>
       </c>
       <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>06/05/2026 8:11:50 AM</t>
+          <t>06/12/2026 9:18:27 AM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8847,7 +8799,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8886,7 +8838,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>06/04/2026 4:43:41 PM</t>
+          <t>06/11/2026 1:13:47 PM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8896,7 +8848,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Christian Davidson</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8911,7 +8863,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G174" t="inlineStr"/>
@@ -8935,7 +8887,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>06/04/2026 2:19:48 PM</t>
+          <t>06/10/2026 2:13:04 PM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8960,7 +8912,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
@@ -8984,32 +8936,28 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>06/04/2026 9:36:08 AM</t>
+          <t>06/10/2026 12:24:28 PM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Roderick Bush</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -9033,32 +8981,32 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>06/03/2026 10:39:43 AM</t>
+          <t>06/10/2026 9:43:39 AM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -9082,32 +9030,32 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>06/02/2026 8:27:02 PM</t>
+          <t>06/10/2026 9:38:39 AM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sebastion Franco</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -9131,7 +9079,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>06/02/2026 6:59:41 PM</t>
+          <t>06/10/2026 8:20:12 AM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9144,11 +9092,7 @@
           <t>Sebastion Franco</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>SLC</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>SLC</t>
@@ -9180,32 +9124,32 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>06/02/2026 2:57:58 PM</t>
+          <t>06/10/2026 7:38:13 AM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 104</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Randy Fennell</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -9219,42 +9163,40 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N180" t="n">
+        <v>0.645</v>
       </c>
       <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>06/02/2026 1:08:52 PM</t>
+          <t>06/09/2026 5:08:17 PM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -9278,27 +9220,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>06/02/2026 12:48:40 PM</t>
+          <t>06/08/2026 4:34:35 PM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Truck 710</t>
+          <t>Truck 78</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>KARVELL OLIVER</t>
+          <t>Mark Varela</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9309,7 +9251,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -9327,27 +9269,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>06/02/2026 11:11:57 AM</t>
+          <t>06/08/2026 11:36:52 AM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 96</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Mark Varela</t>
+          <t>Blake Lewis</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -9376,34 +9318,38 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>06/01/2026 4:28:39 PM</t>
+          <t>06/08/2026 8:30:19 AM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Truck 82</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Michael Reynoso</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SLC</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -9421,32 +9367,32 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>06/01/2026 12:44:20 PM</t>
+          <t>06/05/2026 11:50:44 AM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>Truck 802</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Robert Ulrich</t>
+          <t>James Townsel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>GEG</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -9461,35 +9407,39 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
-        <v>0.516</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>05/29/2026 5:36:46 PM</t>
+          <t>06/05/2026 10:45:18 AM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 84</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Stephen King</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Jose Hondolero</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
@@ -9513,28 +9463,28 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>05/29/2026 5:35:16 PM</t>
+          <t>06/05/2026 9:11:54 AM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Stephen King</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9558,28 +9508,28 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>05/29/2026 12:30:16 PM</t>
+          <t>06/05/2026 8:11:50 AM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Stephen King</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -9603,28 +9553,28 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>05/29/2026 10:22:39 AM</t>
+          <t>06/04/2026 4:43:41 PM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Truck 800</t>
+          <t>TRUCK 74</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Stephen King</t>
+          <t>Sebastion Franco</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>GEG, PDX</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
@@ -9648,38 +9598,38 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>05/28/2026 11:10:28 AM</t>
+          <t>06/04/2026 2:19:48 PM</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Truck 80</t>
+          <t>Truck 711</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Roy Carney</t>
+          <t>Shamonte Jacobs</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -9697,32 +9647,32 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>05/28/2026 7:18:26 AM</t>
+          <t>06/04/2026 9:36:08 AM</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Truck 711</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Shamonte Jacobs</t>
+          <t>Roderick Bush</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -9746,32 +9696,32 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>05/27/2026 1:48:23 PM</t>
+          <t>06/03/2026 10:39:43 AM</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>Truck 82</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
+          <t>Robert Ulrich</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GEG</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
@@ -9785,40 +9735,38 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="n">
-        <v>0.696</v>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>05/27/2026 1:06:15 PM</t>
+          <t>06/02/2026 8:27:02 PM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Truck 75</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Misteer Greene</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
@@ -9832,40 +9780,38 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="n">
-        <v>0.513</v>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>05/26/2026 1:23:21 PM</t>
+          <t>06/02/2026 6:59:41 PM</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Truck 103</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>John Edmonson</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
+          <t>Sebastion Franco</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
@@ -9886,6 +9832,202 @@
       </c>
       <c r="O194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>06/02/2026 2:57:58 PM</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Truck 800</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Robert Ulrich</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>GEG</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>GEG, PDX</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Drowsy</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>06/02/2026 1:08:52 PM</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Truck 800</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Robert Ulrich</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>GEG</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>GEG, PDX</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Drowsy</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>06/02/2026 12:48:40 PM</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Truck 710</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>KARVELL OLIVER</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>06/02/2026 11:11:57 AM</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Truck 75</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mark Varela</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
